--- a/桌宠类产品性能测试记录表.xlsx
+++ b/桌宠类产品性能测试记录表.xlsx
@@ -51,7 +51,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EADCF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -102,6 +132,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -778,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -844,106 +895,752 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>性能类别</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>BongoCat</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Release</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>GitHub Release/本地安装</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>C:\Program Files\BongoCat\bongo-cat.exe；安装包 D:\desktop_pet\BongoCat\BongoCat_1.1.0_x64-setup.exe；源码包 D:\desktop_pet\BongoCat\BongoCat-master.zip</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>exe 直接运行</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>默认动画；记录是否监听键盘/鼠标</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>bongo-cat</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>msedgewebview2</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>默认桌面常驻；采集主进程+WebView2 子进程树</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>实际测试来源为 GitHub 下载的安装包；运行时确认：bongo-cat.exe；子进程 msedgewebview2.exe</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>轻量 2D / WebView 桌宠</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Open LLM Vtuber</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Source</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>源码运行</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Python/Node/模型服务</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>记录模型、麦克风、语音设置</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Desktop Mate</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\Desktop Mate</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>AppID=3301060</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>steam://rungameid/3301060</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>DesktopMate</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>未观察到固定子进程</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>默认模型/默认设置</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>运行时确认：DesktopMate.exe</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>3D / Unity 渲染桌宠</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>P003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Desktop Mate</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>VPet-Simulator</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Steam</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Steam 启动</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>记录 DLC/模型和帧率设置</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\VPet</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>AppID=1920960</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>steam://rungameid/1920960</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>VPet-Simulator.Windows</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>未观察到固定子进程</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>记录模型、插件、帧率设置</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>运行时确认：VPet-Simulator.Windows.exe</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>轻量 2D / WebView 桌宠</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Desktop Goose</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>itch.io</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>C:\Users\zoeuuliu\Downloads\Desktop Goose v0.31\DesktopGoose v0.31\GooseDesktop.exe；来源页 https://samperson.itch.io/desktop-goose；下载包 C:\Users\zoeuuliu\Downloads\Desktop Goose v0.31.zip</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>v0.31</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>itch.io 安装包 / exe 直接运行</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>GooseDesktop</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>未观察到固定子进程</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>记录是否开启恶作剧/文件拖拽等功能</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>已解压到本机 Downloads；运行时确认：GooseDesktop.exe</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>干扰型桌面宠物</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\Ai Vpet</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>AppID=3029820</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>steam://rungameid/3029820</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>UnityCrashHandler64</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>记录 AI/语音/模型设置</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>运行时确认：Ai Vpet.exe；子进程 UnityCrashHandler64.exe</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>AI / WebView / 多进程桌宠</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Tiny Pasture</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\TinyPasture</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>AppID=3167550</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>steam://rungameid/3167550</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>TinyPasture</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>未观察到固定子进程</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>记录显示/窗口/动画设置</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>运行时确认：TinyPasture.exe</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>轻量 2D / WebView 桌宠</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Pocket Waifu:Desktop Pet</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\Pocket Waifu Pet</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>AppID=2989820</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>steam://rungameid/2989820</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>PocketWaifu</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>UnityCrashHandler64</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>记录模型/交互/联网设置</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>运行时确认：PocketWaifu.exe；子进程 UnityCrashHandler64.exe</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>3D / Unity 渲染桌宠</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>AppID=2666510</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>steam://rungameid/2666510</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>UnityCrashHandler64</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>记录是否窗口化/常驻/游戏场景</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>运行时确认：Rusty's Retirement.exe；子进程 UnityCrashHandler64.exe</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>常驻桌面游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>MateEngine</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\MateEngine</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>AppID=3625270</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>steam://rungameid/3625270</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>MateEngineX</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>UnityCrashHandler64</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>记录模型、渲染和 AI 功能设置</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>运行时确认：MateEngineX.exe；子进程 UnityCrashHandler64.exe</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>3D / Unity 渲染桌宠</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Ai桌面宠物</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\AIDesktopPet</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>AppID=4227700</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>steam://rungameid/4227700</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>AIDesktopPet</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>AIDesktopPet 多进程；AI 功能可能拉起 python/pythonw/ffmpeg/node</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>记录 AI/语音/联网/模型设置</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>运行时确认：AIDesktopPet.exe 多进程</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>AI / WebView / 多进程桌宠</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>角落里的艾果 Eggo</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\Eggo</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>AppID=3700760</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>steam://rungameid/3700760</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Eggo</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>未观察到固定子进程</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>记录桌面常驻和交互配置</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>运行时确认：Eggo.exe</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>轻量 2D / WebView 桌宠</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Molili Ai Friends: Ai 桌面宠物</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\Molili</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>AppID=4141770</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>steam://rungameid/4141770</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Molili</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>msedgewebview2</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>记录 AI/语音/联网/模型设置</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>运行时确认：Molili.exe；子进程 msedgewebview2.exe</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>AI / WebView / 多进程桌宠</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>猫娘计划 - N.E.K.O</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>C:\Program Files (x86)\Steam\steamapps\common\n.e.k.o</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>AppID=4099310</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>steam://rungameid/4099310</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>N.E.K.O</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>N.E.K.O 多进程；projectneko_server/openfang</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>记录桌面常驻、模型和交互配置</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>运行时确认：N.E.K.O.exe 多进程；子进程 projectneko_server.exe、openfang.exe</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>AI / WebView / 多进程桌宠</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1171,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AB92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1347,1012 +2044,4372 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>BongoCat</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>系统基线</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
+      <c r="N2" s="6" t="n"/>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="6" t="n"/>
+      <c r="Q2" s="6" t="n"/>
+      <c r="R2" s="6" t="n"/>
+      <c r="S2" s="6" t="n"/>
+      <c r="T2" s="6" t="n"/>
+      <c r="U2" s="6" t="n"/>
+      <c r="V2" s="6" t="n"/>
+      <c r="W2" s="6" t="n"/>
+      <c r="X2" s="6" t="n"/>
+      <c r="Y2" s="6" t="n"/>
+      <c r="Z2" s="6" t="n"/>
+      <c r="AA2" s="6" t="n"/>
+      <c r="AB2" s="6" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>BongoCat</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>启动峰值</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr"/>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr"/>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+      <c r="N3" s="6" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="6" t="n"/>
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="6" t="n"/>
+      <c r="T3" s="6" t="n"/>
+      <c r="U3" s="6" t="n"/>
+      <c r="V3" s="6" t="n"/>
+      <c r="W3" s="6" t="n"/>
+      <c r="X3" s="6" t="n"/>
+      <c r="Y3" s="6" t="n"/>
+      <c r="Z3" s="6" t="n"/>
+      <c r="AA3" s="6" t="n"/>
+      <c r="AB3" s="6" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>BongoCat</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>空闲常驻</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
-      <c r="Z4" s="4" t="inlineStr"/>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
+      <c r="T4" s="6" t="n"/>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="n"/>
+      <c r="Y4" s="6" t="n"/>
+      <c r="Z4" s="6" t="n"/>
+      <c r="AA4" s="6" t="n"/>
+      <c r="AB4" s="6" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>R004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>BongoCat</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>基础交互</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr"/>
-      <c r="Z5" s="4" t="inlineStr"/>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="6" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
+      <c r="Z5" s="6" t="n"/>
+      <c r="AA5" s="6" t="n"/>
+      <c r="AB5" s="6" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>R005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>BongoCat</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>功能开启</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
-      <c r="Z6" s="4" t="inlineStr"/>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="n"/>
+      <c r="Y6" s="6" t="n"/>
+      <c r="Z6" s="6" t="n"/>
+      <c r="AA6" s="6" t="n"/>
+      <c r="AB6" s="6" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>R006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>BongoCat</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>长时间稳定</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
+      <c r="Z7" s="6" t="n"/>
+      <c r="AA7" s="6" t="n"/>
+      <c r="AB7" s="6" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>R007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>P001</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>BongoCat</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>游戏影响</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr"/>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
+      <c r="Z8" s="6" t="n"/>
+      <c r="AA8" s="6" t="n"/>
+      <c r="AB8" s="6" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>R008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Open LLM Vtuber</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Desktop Mate</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>系统基线</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="7" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="7" t="n"/>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
+      <c r="W9" s="7" t="n"/>
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="7" t="n"/>
+      <c r="Z9" s="7" t="n"/>
+      <c r="AA9" s="7" t="n"/>
+      <c r="AB9" s="7" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>R009</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Open LLM Vtuber</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Desktop Mate</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>启动峰值</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="4" t="inlineStr"/>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
+      <c r="O10" s="7" t="n"/>
+      <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="7" t="n"/>
+      <c r="T10" s="7" t="n"/>
+      <c r="U10" s="7" t="n"/>
+      <c r="V10" s="7" t="n"/>
+      <c r="W10" s="7" t="n"/>
+      <c r="X10" s="7" t="n"/>
+      <c r="Y10" s="7" t="n"/>
+      <c r="Z10" s="7" t="n"/>
+      <c r="AA10" s="7" t="n"/>
+      <c r="AB10" s="7" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>R010</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Open LLM Vtuber</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Desktop Mate</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>空闲常驻</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="4" t="inlineStr"/>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="7" t="n"/>
+      <c r="O11" s="7" t="n"/>
+      <c r="P11" s="7" t="n"/>
+      <c r="Q11" s="7" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="7" t="n"/>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
+      <c r="W11" s="7" t="n"/>
+      <c r="X11" s="7" t="n"/>
+      <c r="Y11" s="7" t="n"/>
+      <c r="Z11" s="7" t="n"/>
+      <c r="AA11" s="7" t="n"/>
+      <c r="AB11" s="7" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>R011</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Open LLM Vtuber</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Desktop Mate</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>基础交互</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="4" t="inlineStr"/>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
+      <c r="O12" s="7" t="n"/>
+      <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="S12" s="7" t="n"/>
+      <c r="T12" s="7" t="n"/>
+      <c r="U12" s="7" t="n"/>
+      <c r="V12" s="7" t="n"/>
+      <c r="W12" s="7" t="n"/>
+      <c r="X12" s="7" t="n"/>
+      <c r="Y12" s="7" t="n"/>
+      <c r="Z12" s="7" t="n"/>
+      <c r="AA12" s="7" t="n"/>
+      <c r="AB12" s="7" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>R012</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Open LLM Vtuber</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Desktop Mate</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>功能开启</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="inlineStr"/>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr"/>
-      <c r="Z13" s="4" t="inlineStr"/>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="7" t="n"/>
+      <c r="O13" s="7" t="n"/>
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="7" t="n"/>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
+      <c r="W13" s="7" t="n"/>
+      <c r="X13" s="7" t="n"/>
+      <c r="Y13" s="7" t="n"/>
+      <c r="Z13" s="7" t="n"/>
+      <c r="AA13" s="7" t="n"/>
+      <c r="AB13" s="7" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>R013</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Open LLM Vtuber</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Desktop Mate</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>长时间稳定</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="4" t="inlineStr"/>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
+      <c r="O14" s="7" t="n"/>
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="7" t="n"/>
+      <c r="T14" s="7" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="n"/>
+      <c r="Y14" s="7" t="n"/>
+      <c r="Z14" s="7" t="n"/>
+      <c r="AA14" s="7" t="n"/>
+      <c r="AB14" s="7" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>R014</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>P002</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Open LLM Vtuber</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Desktop Mate</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>游戏影响</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="inlineStr"/>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="inlineStr"/>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr"/>
-      <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="7" t="n"/>
+      <c r="O15" s="7" t="n"/>
+      <c r="P15" s="7" t="n"/>
+      <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="7" t="n"/>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
+      <c r="W15" s="7" t="n"/>
+      <c r="X15" s="7" t="n"/>
+      <c r="Y15" s="7" t="n"/>
+      <c r="Z15" s="7" t="n"/>
+      <c r="AA15" s="7" t="n"/>
+      <c r="AB15" s="7" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>R015</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>P003</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Desktop Mate</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>VPet-Simulator</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>系统基线</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr"/>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr"/>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="6" t="n"/>
+      <c r="T16" s="6" t="n"/>
+      <c r="U16" s="6" t="n"/>
+      <c r="V16" s="6" t="n"/>
+      <c r="W16" s="6" t="n"/>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="6" t="n"/>
+      <c r="Z16" s="6" t="n"/>
+      <c r="AA16" s="6" t="n"/>
+      <c r="AB16" s="6" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>R016</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>P003</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Desktop Mate</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>VPet-Simulator</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>启动峰值</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="inlineStr"/>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="inlineStr"/>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
+      <c r="T17" s="6" t="n"/>
+      <c r="U17" s="6" t="n"/>
+      <c r="V17" s="6" t="n"/>
+      <c r="W17" s="6" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
+      <c r="Z17" s="6" t="n"/>
+      <c r="AA17" s="6" t="n"/>
+      <c r="AB17" s="6" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>R017</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>P003</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Desktop Mate</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>VPet-Simulator</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>空闲常驻</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="inlineStr"/>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr"/>
-      <c r="Y18" s="4" t="inlineStr"/>
-      <c r="Z18" s="4" t="inlineStr"/>
-      <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="n"/>
+      <c r="T18" s="6" t="n"/>
+      <c r="U18" s="6" t="n"/>
+      <c r="V18" s="6" t="n"/>
+      <c r="W18" s="6" t="n"/>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="6" t="n"/>
+      <c r="Z18" s="6" t="n"/>
+      <c r="AA18" s="6" t="n"/>
+      <c r="AB18" s="6" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>R018</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>P003</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Desktop Mate</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>VPet-Simulator</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>基础交互</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="inlineStr"/>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="4" t="inlineStr"/>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
+      <c r="T19" s="6" t="n"/>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="6" t="n"/>
+      <c r="W19" s="6" t="n"/>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
+      <c r="Z19" s="6" t="n"/>
+      <c r="AA19" s="6" t="n"/>
+      <c r="AB19" s="6" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>R019</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>P003</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Desktop Mate</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>VPet-Simulator</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>功能开启</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="inlineStr"/>
-      <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="4" t="inlineStr"/>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n"/>
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="6" t="n"/>
+      <c r="T20" s="6" t="n"/>
+      <c r="U20" s="6" t="n"/>
+      <c r="V20" s="6" t="n"/>
+      <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
+      <c r="Z20" s="6" t="n"/>
+      <c r="AA20" s="6" t="n"/>
+      <c r="AB20" s="6" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>R020</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>P003</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Desktop Mate</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>VPet-Simulator</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>长时间稳定</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="inlineStr"/>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="4" t="inlineStr"/>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr"/>
-      <c r="Y21" s="4" t="inlineStr"/>
-      <c r="Z21" s="4" t="inlineStr"/>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="n"/>
+      <c r="T21" s="6" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
+      <c r="Z21" s="6" t="n"/>
+      <c r="AA21" s="6" t="n"/>
+      <c r="AB21" s="6" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>R021</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>P003</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Desktop Mate</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>VPet-Simulator</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>游戏影响</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr"/>
-      <c r="O22" s="4" t="inlineStr"/>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="inlineStr"/>
-      <c r="W22" s="4" t="inlineStr"/>
-      <c r="X22" s="4" t="inlineStr"/>
-      <c r="Y22" s="4" t="inlineStr"/>
-      <c r="Z22" s="4" t="inlineStr"/>
-      <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="inlineStr"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="6" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="6" t="n"/>
+      <c r="AA22" s="6" t="n"/>
+      <c r="AB22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>R022</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Desktop Goose</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="n"/>
+      <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="8" t="n"/>
+      <c r="R23" s="8" t="n"/>
+      <c r="S23" s="8" t="n"/>
+      <c r="T23" s="8" t="n"/>
+      <c r="U23" s="8" t="n"/>
+      <c r="V23" s="8" t="n"/>
+      <c r="W23" s="8" t="n"/>
+      <c r="X23" s="8" t="n"/>
+      <c r="Y23" s="8" t="n"/>
+      <c r="Z23" s="8" t="n"/>
+      <c r="AA23" s="8" t="n"/>
+      <c r="AB23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>R023</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Desktop Goose</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="8" t="n"/>
+      <c r="S24" s="8" t="n"/>
+      <c r="T24" s="8" t="n"/>
+      <c r="U24" s="8" t="n"/>
+      <c r="V24" s="8" t="n"/>
+      <c r="W24" s="8" t="n"/>
+      <c r="X24" s="8" t="n"/>
+      <c r="Y24" s="8" t="n"/>
+      <c r="Z24" s="8" t="n"/>
+      <c r="AA24" s="8" t="n"/>
+      <c r="AB24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>R024</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Desktop Goose</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+      <c r="L25" s="8" t="n"/>
+      <c r="M25" s="8" t="n"/>
+      <c r="N25" s="8" t="n"/>
+      <c r="O25" s="8" t="n"/>
+      <c r="P25" s="8" t="n"/>
+      <c r="Q25" s="8" t="n"/>
+      <c r="R25" s="8" t="n"/>
+      <c r="S25" s="8" t="n"/>
+      <c r="T25" s="8" t="n"/>
+      <c r="U25" s="8" t="n"/>
+      <c r="V25" s="8" t="n"/>
+      <c r="W25" s="8" t="n"/>
+      <c r="X25" s="8" t="n"/>
+      <c r="Y25" s="8" t="n"/>
+      <c r="Z25" s="8" t="n"/>
+      <c r="AA25" s="8" t="n"/>
+      <c r="AB25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>R025</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Desktop Goose</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="8" t="n"/>
+      <c r="O26" s="8" t="n"/>
+      <c r="P26" s="8" t="n"/>
+      <c r="Q26" s="8" t="n"/>
+      <c r="R26" s="8" t="n"/>
+      <c r="S26" s="8" t="n"/>
+      <c r="T26" s="8" t="n"/>
+      <c r="U26" s="8" t="n"/>
+      <c r="V26" s="8" t="n"/>
+      <c r="W26" s="8" t="n"/>
+      <c r="X26" s="8" t="n"/>
+      <c r="Y26" s="8" t="n"/>
+      <c r="Z26" s="8" t="n"/>
+      <c r="AA26" s="8" t="n"/>
+      <c r="AB26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>R026</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Desktop Goose</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
+      <c r="M27" s="8" t="n"/>
+      <c r="N27" s="8" t="n"/>
+      <c r="O27" s="8" t="n"/>
+      <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="8" t="n"/>
+      <c r="R27" s="8" t="n"/>
+      <c r="S27" s="8" t="n"/>
+      <c r="T27" s="8" t="n"/>
+      <c r="U27" s="8" t="n"/>
+      <c r="V27" s="8" t="n"/>
+      <c r="W27" s="8" t="n"/>
+      <c r="X27" s="8" t="n"/>
+      <c r="Y27" s="8" t="n"/>
+      <c r="Z27" s="8" t="n"/>
+      <c r="AA27" s="8" t="n"/>
+      <c r="AB27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>R027</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Desktop Goose</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="n"/>
+      <c r="P28" s="8" t="n"/>
+      <c r="Q28" s="8" t="n"/>
+      <c r="R28" s="8" t="n"/>
+      <c r="S28" s="8" t="n"/>
+      <c r="T28" s="8" t="n"/>
+      <c r="U28" s="8" t="n"/>
+      <c r="V28" s="8" t="n"/>
+      <c r="W28" s="8" t="n"/>
+      <c r="X28" s="8" t="n"/>
+      <c r="Y28" s="8" t="n"/>
+      <c r="Z28" s="8" t="n"/>
+      <c r="AA28" s="8" t="n"/>
+      <c r="AB28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>R028</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Desktop Goose</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="8" t="n"/>
+      <c r="O29" s="8" t="n"/>
+      <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="8" t="n"/>
+      <c r="R29" s="8" t="n"/>
+      <c r="S29" s="8" t="n"/>
+      <c r="T29" s="8" t="n"/>
+      <c r="U29" s="8" t="n"/>
+      <c r="V29" s="8" t="n"/>
+      <c r="W29" s="8" t="n"/>
+      <c r="X29" s="8" t="n"/>
+      <c r="Y29" s="8" t="n"/>
+      <c r="Z29" s="8" t="n"/>
+      <c r="AA29" s="8" t="n"/>
+      <c r="AB29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>R029</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="9" t="n"/>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="9" t="n"/>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="9" t="n"/>
+      <c r="Q30" s="9" t="n"/>
+      <c r="R30" s="9" t="n"/>
+      <c r="S30" s="9" t="n"/>
+      <c r="T30" s="9" t="n"/>
+      <c r="U30" s="9" t="n"/>
+      <c r="V30" s="9" t="n"/>
+      <c r="W30" s="9" t="n"/>
+      <c r="X30" s="9" t="n"/>
+      <c r="Y30" s="9" t="n"/>
+      <c r="Z30" s="9" t="n"/>
+      <c r="AA30" s="9" t="n"/>
+      <c r="AB30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>R030</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
+      <c r="L31" s="9" t="n"/>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="9" t="n"/>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="9" t="n"/>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="9" t="n"/>
+      <c r="S31" s="9" t="n"/>
+      <c r="T31" s="9" t="n"/>
+      <c r="U31" s="9" t="n"/>
+      <c r="V31" s="9" t="n"/>
+      <c r="W31" s="9" t="n"/>
+      <c r="X31" s="9" t="n"/>
+      <c r="Y31" s="9" t="n"/>
+      <c r="Z31" s="9" t="n"/>
+      <c r="AA31" s="9" t="n"/>
+      <c r="AB31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>R031</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="n"/>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="9" t="n"/>
+      <c r="Q32" s="9" t="n"/>
+      <c r="R32" s="9" t="n"/>
+      <c r="S32" s="9" t="n"/>
+      <c r="T32" s="9" t="n"/>
+      <c r="U32" s="9" t="n"/>
+      <c r="V32" s="9" t="n"/>
+      <c r="W32" s="9" t="n"/>
+      <c r="X32" s="9" t="n"/>
+      <c r="Y32" s="9" t="n"/>
+      <c r="Z32" s="9" t="n"/>
+      <c r="AA32" s="9" t="n"/>
+      <c r="AB32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>R032</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="9" t="n"/>
+      <c r="S33" s="9" t="n"/>
+      <c r="T33" s="9" t="n"/>
+      <c r="U33" s="9" t="n"/>
+      <c r="V33" s="9" t="n"/>
+      <c r="W33" s="9" t="n"/>
+      <c r="X33" s="9" t="n"/>
+      <c r="Y33" s="9" t="n"/>
+      <c r="Z33" s="9" t="n"/>
+      <c r="AA33" s="9" t="n"/>
+      <c r="AB33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>R033</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="9" t="n"/>
+      <c r="M34" s="9" t="n"/>
+      <c r="N34" s="9" t="n"/>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="9" t="n"/>
+      <c r="S34" s="9" t="n"/>
+      <c r="T34" s="9" t="n"/>
+      <c r="U34" s="9" t="n"/>
+      <c r="V34" s="9" t="n"/>
+      <c r="W34" s="9" t="n"/>
+      <c r="X34" s="9" t="n"/>
+      <c r="Y34" s="9" t="n"/>
+      <c r="Z34" s="9" t="n"/>
+      <c r="AA34" s="9" t="n"/>
+      <c r="AB34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>R034</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="9" t="n"/>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n"/>
+      <c r="Z35" s="9" t="n"/>
+      <c r="AA35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>R035</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="9" t="n"/>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="9" t="n"/>
+      <c r="P36" s="9" t="n"/>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="9" t="n"/>
+      <c r="S36" s="9" t="n"/>
+      <c r="T36" s="9" t="n"/>
+      <c r="U36" s="9" t="n"/>
+      <c r="V36" s="9" t="n"/>
+      <c r="W36" s="9" t="n"/>
+      <c r="X36" s="9" t="n"/>
+      <c r="Y36" s="9" t="n"/>
+      <c r="Z36" s="9" t="n"/>
+      <c r="AA36" s="9" t="n"/>
+      <c r="AB36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>R036</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Tiny Pasture</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="n"/>
+      <c r="Q37" s="6" t="n"/>
+      <c r="R37" s="6" t="n"/>
+      <c r="S37" s="6" t="n"/>
+      <c r="T37" s="6" t="n"/>
+      <c r="U37" s="6" t="n"/>
+      <c r="V37" s="6" t="n"/>
+      <c r="W37" s="6" t="n"/>
+      <c r="X37" s="6" t="n"/>
+      <c r="Y37" s="6" t="n"/>
+      <c r="Z37" s="6" t="n"/>
+      <c r="AA37" s="6" t="n"/>
+      <c r="AB37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>R037</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Tiny Pasture</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="6" t="n"/>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
+      <c r="N38" s="6" t="n"/>
+      <c r="O38" s="6" t="n"/>
+      <c r="P38" s="6" t="n"/>
+      <c r="Q38" s="6" t="n"/>
+      <c r="R38" s="6" t="n"/>
+      <c r="S38" s="6" t="n"/>
+      <c r="T38" s="6" t="n"/>
+      <c r="U38" s="6" t="n"/>
+      <c r="V38" s="6" t="n"/>
+      <c r="W38" s="6" t="n"/>
+      <c r="X38" s="6" t="n"/>
+      <c r="Y38" s="6" t="n"/>
+      <c r="Z38" s="6" t="n"/>
+      <c r="AA38" s="6" t="n"/>
+      <c r="AB38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>R038</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Tiny Pasture</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="6" t="n"/>
+      <c r="M39" s="6" t="n"/>
+      <c r="N39" s="6" t="n"/>
+      <c r="O39" s="6" t="n"/>
+      <c r="P39" s="6" t="n"/>
+      <c r="Q39" s="6" t="n"/>
+      <c r="R39" s="6" t="n"/>
+      <c r="S39" s="6" t="n"/>
+      <c r="T39" s="6" t="n"/>
+      <c r="U39" s="6" t="n"/>
+      <c r="V39" s="6" t="n"/>
+      <c r="W39" s="6" t="n"/>
+      <c r="X39" s="6" t="n"/>
+      <c r="Y39" s="6" t="n"/>
+      <c r="Z39" s="6" t="n"/>
+      <c r="AA39" s="6" t="n"/>
+      <c r="AB39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>R039</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Tiny Pasture</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="6" t="n"/>
+      <c r="O40" s="6" t="n"/>
+      <c r="P40" s="6" t="n"/>
+      <c r="Q40" s="6" t="n"/>
+      <c r="R40" s="6" t="n"/>
+      <c r="S40" s="6" t="n"/>
+      <c r="T40" s="6" t="n"/>
+      <c r="U40" s="6" t="n"/>
+      <c r="V40" s="6" t="n"/>
+      <c r="W40" s="6" t="n"/>
+      <c r="X40" s="6" t="n"/>
+      <c r="Y40" s="6" t="n"/>
+      <c r="Z40" s="6" t="n"/>
+      <c r="AA40" s="6" t="n"/>
+      <c r="AB40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>R040</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Tiny Pasture</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="6" t="n"/>
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="6" t="n"/>
+      <c r="Q41" s="6" t="n"/>
+      <c r="R41" s="6" t="n"/>
+      <c r="S41" s="6" t="n"/>
+      <c r="T41" s="6" t="n"/>
+      <c r="U41" s="6" t="n"/>
+      <c r="V41" s="6" t="n"/>
+      <c r="W41" s="6" t="n"/>
+      <c r="X41" s="6" t="n"/>
+      <c r="Y41" s="6" t="n"/>
+      <c r="Z41" s="6" t="n"/>
+      <c r="AA41" s="6" t="n"/>
+      <c r="AB41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>R041</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Tiny Pasture</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="6" t="n"/>
+      <c r="O42" s="6" t="n"/>
+      <c r="P42" s="6" t="n"/>
+      <c r="Q42" s="6" t="n"/>
+      <c r="R42" s="6" t="n"/>
+      <c r="S42" s="6" t="n"/>
+      <c r="T42" s="6" t="n"/>
+      <c r="U42" s="6" t="n"/>
+      <c r="V42" s="6" t="n"/>
+      <c r="W42" s="6" t="n"/>
+      <c r="X42" s="6" t="n"/>
+      <c r="Y42" s="6" t="n"/>
+      <c r="Z42" s="6" t="n"/>
+      <c r="AA42" s="6" t="n"/>
+      <c r="AB42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>R042</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Tiny Pasture</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
+      <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="6" t="n"/>
+      <c r="O43" s="6" t="n"/>
+      <c r="P43" s="6" t="n"/>
+      <c r="Q43" s="6" t="n"/>
+      <c r="R43" s="6" t="n"/>
+      <c r="S43" s="6" t="n"/>
+      <c r="T43" s="6" t="n"/>
+      <c r="U43" s="6" t="n"/>
+      <c r="V43" s="6" t="n"/>
+      <c r="W43" s="6" t="n"/>
+      <c r="X43" s="6" t="n"/>
+      <c r="Y43" s="6" t="n"/>
+      <c r="Z43" s="6" t="n"/>
+      <c r="AA43" s="6" t="n"/>
+      <c r="AB43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>R043</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Pocket Waifu:Desktop Pet</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
+      <c r="P44" s="7" t="n"/>
+      <c r="Q44" s="7" t="n"/>
+      <c r="R44" s="7" t="n"/>
+      <c r="S44" s="7" t="n"/>
+      <c r="T44" s="7" t="n"/>
+      <c r="U44" s="7" t="n"/>
+      <c r="V44" s="7" t="n"/>
+      <c r="W44" s="7" t="n"/>
+      <c r="X44" s="7" t="n"/>
+      <c r="Y44" s="7" t="n"/>
+      <c r="Z44" s="7" t="n"/>
+      <c r="AA44" s="7" t="n"/>
+      <c r="AB44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>R044</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Pocket Waifu:Desktop Pet</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="7" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="7" t="n"/>
+      <c r="P45" s="7" t="n"/>
+      <c r="Q45" s="7" t="n"/>
+      <c r="R45" s="7" t="n"/>
+      <c r="S45" s="7" t="n"/>
+      <c r="T45" s="7" t="n"/>
+      <c r="U45" s="7" t="n"/>
+      <c r="V45" s="7" t="n"/>
+      <c r="W45" s="7" t="n"/>
+      <c r="X45" s="7" t="n"/>
+      <c r="Y45" s="7" t="n"/>
+      <c r="Z45" s="7" t="n"/>
+      <c r="AA45" s="7" t="n"/>
+      <c r="AB45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>R045</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Pocket Waifu:Desktop Pet</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
+      <c r="J46" s="7" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="7" t="n"/>
+      <c r="P46" s="7" t="n"/>
+      <c r="Q46" s="7" t="n"/>
+      <c r="R46" s="7" t="n"/>
+      <c r="S46" s="7" t="n"/>
+      <c r="T46" s="7" t="n"/>
+      <c r="U46" s="7" t="n"/>
+      <c r="V46" s="7" t="n"/>
+      <c r="W46" s="7" t="n"/>
+      <c r="X46" s="7" t="n"/>
+      <c r="Y46" s="7" t="n"/>
+      <c r="Z46" s="7" t="n"/>
+      <c r="AA46" s="7" t="n"/>
+      <c r="AB46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>R046</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Pocket Waifu:Desktop Pet</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="7" t="n"/>
+      <c r="P47" s="7" t="n"/>
+      <c r="Q47" s="7" t="n"/>
+      <c r="R47" s="7" t="n"/>
+      <c r="S47" s="7" t="n"/>
+      <c r="T47" s="7" t="n"/>
+      <c r="U47" s="7" t="n"/>
+      <c r="V47" s="7" t="n"/>
+      <c r="W47" s="7" t="n"/>
+      <c r="X47" s="7" t="n"/>
+      <c r="Y47" s="7" t="n"/>
+      <c r="Z47" s="7" t="n"/>
+      <c r="AA47" s="7" t="n"/>
+      <c r="AB47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>R047</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Pocket Waifu:Desktop Pet</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+      <c r="J48" s="7" t="n"/>
+      <c r="K48" s="7" t="n"/>
+      <c r="L48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
+      <c r="N48" s="7" t="n"/>
+      <c r="O48" s="7" t="n"/>
+      <c r="P48" s="7" t="n"/>
+      <c r="Q48" s="7" t="n"/>
+      <c r="R48" s="7" t="n"/>
+      <c r="S48" s="7" t="n"/>
+      <c r="T48" s="7" t="n"/>
+      <c r="U48" s="7" t="n"/>
+      <c r="V48" s="7" t="n"/>
+      <c r="W48" s="7" t="n"/>
+      <c r="X48" s="7" t="n"/>
+      <c r="Y48" s="7" t="n"/>
+      <c r="Z48" s="7" t="n"/>
+      <c r="AA48" s="7" t="n"/>
+      <c r="AB48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>R048</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Pocket Waifu:Desktop Pet</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+      <c r="J49" s="7" t="n"/>
+      <c r="K49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
+      <c r="N49" s="7" t="n"/>
+      <c r="O49" s="7" t="n"/>
+      <c r="P49" s="7" t="n"/>
+      <c r="Q49" s="7" t="n"/>
+      <c r="R49" s="7" t="n"/>
+      <c r="S49" s="7" t="n"/>
+      <c r="T49" s="7" t="n"/>
+      <c r="U49" s="7" t="n"/>
+      <c r="V49" s="7" t="n"/>
+      <c r="W49" s="7" t="n"/>
+      <c r="X49" s="7" t="n"/>
+      <c r="Y49" s="7" t="n"/>
+      <c r="Z49" s="7" t="n"/>
+      <c r="AA49" s="7" t="n"/>
+      <c r="AB49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>R049</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Pocket Waifu:Desktop Pet</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="7" t="n"/>
+      <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
+      <c r="N50" s="7" t="n"/>
+      <c r="O50" s="7" t="n"/>
+      <c r="P50" s="7" t="n"/>
+      <c r="Q50" s="7" t="n"/>
+      <c r="R50" s="7" t="n"/>
+      <c r="S50" s="7" t="n"/>
+      <c r="T50" s="7" t="n"/>
+      <c r="U50" s="7" t="n"/>
+      <c r="V50" s="7" t="n"/>
+      <c r="W50" s="7" t="n"/>
+      <c r="X50" s="7" t="n"/>
+      <c r="Y50" s="7" t="n"/>
+      <c r="Z50" s="7" t="n"/>
+      <c r="AA50" s="7" t="n"/>
+      <c r="AB50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>R050</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="10" t="n"/>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="10" t="n"/>
+      <c r="Y51" s="10" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>R051</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="10" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="10" t="n"/>
+      <c r="Y52" s="10" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>R052</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="10" t="n"/>
+      <c r="Y53" s="10" t="n"/>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>R053</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>R054</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
+      <c r="Y55" s="10" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>R055</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="10" t="n"/>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="10" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="n"/>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="10" t="n"/>
+      <c r="X56" s="10" t="n"/>
+      <c r="Y56" s="10" t="n"/>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>R056</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>R057</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>MateEngine</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+      <c r="J58" s="7" t="n"/>
+      <c r="K58" s="7" t="n"/>
+      <c r="L58" s="7" t="n"/>
+      <c r="M58" s="7" t="n"/>
+      <c r="N58" s="7" t="n"/>
+      <c r="O58" s="7" t="n"/>
+      <c r="P58" s="7" t="n"/>
+      <c r="Q58" s="7" t="n"/>
+      <c r="R58" s="7" t="n"/>
+      <c r="S58" s="7" t="n"/>
+      <c r="T58" s="7" t="n"/>
+      <c r="U58" s="7" t="n"/>
+      <c r="V58" s="7" t="n"/>
+      <c r="W58" s="7" t="n"/>
+      <c r="X58" s="7" t="n"/>
+      <c r="Y58" s="7" t="n"/>
+      <c r="Z58" s="7" t="n"/>
+      <c r="AA58" s="7" t="n"/>
+      <c r="AB58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>R058</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>MateEngine</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
+      <c r="J59" s="7" t="n"/>
+      <c r="K59" s="7" t="n"/>
+      <c r="L59" s="7" t="n"/>
+      <c r="M59" s="7" t="n"/>
+      <c r="N59" s="7" t="n"/>
+      <c r="O59" s="7" t="n"/>
+      <c r="P59" s="7" t="n"/>
+      <c r="Q59" s="7" t="n"/>
+      <c r="R59" s="7" t="n"/>
+      <c r="S59" s="7" t="n"/>
+      <c r="T59" s="7" t="n"/>
+      <c r="U59" s="7" t="n"/>
+      <c r="V59" s="7" t="n"/>
+      <c r="W59" s="7" t="n"/>
+      <c r="X59" s="7" t="n"/>
+      <c r="Y59" s="7" t="n"/>
+      <c r="Z59" s="7" t="n"/>
+      <c r="AA59" s="7" t="n"/>
+      <c r="AB59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>R059</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>MateEngine</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
+      <c r="K60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
+      <c r="N60" s="7" t="n"/>
+      <c r="O60" s="7" t="n"/>
+      <c r="P60" s="7" t="n"/>
+      <c r="Q60" s="7" t="n"/>
+      <c r="R60" s="7" t="n"/>
+      <c r="S60" s="7" t="n"/>
+      <c r="T60" s="7" t="n"/>
+      <c r="U60" s="7" t="n"/>
+      <c r="V60" s="7" t="n"/>
+      <c r="W60" s="7" t="n"/>
+      <c r="X60" s="7" t="n"/>
+      <c r="Y60" s="7" t="n"/>
+      <c r="Z60" s="7" t="n"/>
+      <c r="AA60" s="7" t="n"/>
+      <c r="AB60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>R060</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>MateEngine</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="7" t="n"/>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+      <c r="J61" s="7" t="n"/>
+      <c r="K61" s="7" t="n"/>
+      <c r="L61" s="7" t="n"/>
+      <c r="M61" s="7" t="n"/>
+      <c r="N61" s="7" t="n"/>
+      <c r="O61" s="7" t="n"/>
+      <c r="P61" s="7" t="n"/>
+      <c r="Q61" s="7" t="n"/>
+      <c r="R61" s="7" t="n"/>
+      <c r="S61" s="7" t="n"/>
+      <c r="T61" s="7" t="n"/>
+      <c r="U61" s="7" t="n"/>
+      <c r="V61" s="7" t="n"/>
+      <c r="W61" s="7" t="n"/>
+      <c r="X61" s="7" t="n"/>
+      <c r="Y61" s="7" t="n"/>
+      <c r="Z61" s="7" t="n"/>
+      <c r="AA61" s="7" t="n"/>
+      <c r="AB61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>R061</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>MateEngine</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="7" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+      <c r="J62" s="7" t="n"/>
+      <c r="K62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
+      <c r="N62" s="7" t="n"/>
+      <c r="O62" s="7" t="n"/>
+      <c r="P62" s="7" t="n"/>
+      <c r="Q62" s="7" t="n"/>
+      <c r="R62" s="7" t="n"/>
+      <c r="S62" s="7" t="n"/>
+      <c r="T62" s="7" t="n"/>
+      <c r="U62" s="7" t="n"/>
+      <c r="V62" s="7" t="n"/>
+      <c r="W62" s="7" t="n"/>
+      <c r="X62" s="7" t="n"/>
+      <c r="Y62" s="7" t="n"/>
+      <c r="Z62" s="7" t="n"/>
+      <c r="AA62" s="7" t="n"/>
+      <c r="AB62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>R062</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>MateEngine</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+      <c r="J63" s="7" t="n"/>
+      <c r="K63" s="7" t="n"/>
+      <c r="L63" s="7" t="n"/>
+      <c r="M63" s="7" t="n"/>
+      <c r="N63" s="7" t="n"/>
+      <c r="O63" s="7" t="n"/>
+      <c r="P63" s="7" t="n"/>
+      <c r="Q63" s="7" t="n"/>
+      <c r="R63" s="7" t="n"/>
+      <c r="S63" s="7" t="n"/>
+      <c r="T63" s="7" t="n"/>
+      <c r="U63" s="7" t="n"/>
+      <c r="V63" s="7" t="n"/>
+      <c r="W63" s="7" t="n"/>
+      <c r="X63" s="7" t="n"/>
+      <c r="Y63" s="7" t="n"/>
+      <c r="Z63" s="7" t="n"/>
+      <c r="AA63" s="7" t="n"/>
+      <c r="AB63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>R063</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>MateEngine</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+      <c r="J64" s="7" t="n"/>
+      <c r="K64" s="7" t="n"/>
+      <c r="L64" s="7" t="n"/>
+      <c r="M64" s="7" t="n"/>
+      <c r="N64" s="7" t="n"/>
+      <c r="O64" s="7" t="n"/>
+      <c r="P64" s="7" t="n"/>
+      <c r="Q64" s="7" t="n"/>
+      <c r="R64" s="7" t="n"/>
+      <c r="S64" s="7" t="n"/>
+      <c r="T64" s="7" t="n"/>
+      <c r="U64" s="7" t="n"/>
+      <c r="V64" s="7" t="n"/>
+      <c r="W64" s="7" t="n"/>
+      <c r="X64" s="7" t="n"/>
+      <c r="Y64" s="7" t="n"/>
+      <c r="Z64" s="7" t="n"/>
+      <c r="AA64" s="7" t="n"/>
+      <c r="AB64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>R064</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Ai桌面宠物</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="n"/>
+      <c r="H65" s="9" t="n"/>
+      <c r="I65" s="9" t="n"/>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="9" t="n"/>
+      <c r="N65" s="9" t="n"/>
+      <c r="O65" s="9" t="n"/>
+      <c r="P65" s="9" t="n"/>
+      <c r="Q65" s="9" t="n"/>
+      <c r="R65" s="9" t="n"/>
+      <c r="S65" s="9" t="n"/>
+      <c r="T65" s="9" t="n"/>
+      <c r="U65" s="9" t="n"/>
+      <c r="V65" s="9" t="n"/>
+      <c r="W65" s="9" t="n"/>
+      <c r="X65" s="9" t="n"/>
+      <c r="Y65" s="9" t="n"/>
+      <c r="Z65" s="9" t="n"/>
+      <c r="AA65" s="9" t="n"/>
+      <c r="AB65" s="9" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>R065</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Ai桌面宠物</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="n"/>
+      <c r="I66" s="9" t="n"/>
+      <c r="J66" s="9" t="n"/>
+      <c r="K66" s="9" t="n"/>
+      <c r="L66" s="9" t="n"/>
+      <c r="M66" s="9" t="n"/>
+      <c r="N66" s="9" t="n"/>
+      <c r="O66" s="9" t="n"/>
+      <c r="P66" s="9" t="n"/>
+      <c r="Q66" s="9" t="n"/>
+      <c r="R66" s="9" t="n"/>
+      <c r="S66" s="9" t="n"/>
+      <c r="T66" s="9" t="n"/>
+      <c r="U66" s="9" t="n"/>
+      <c r="V66" s="9" t="n"/>
+      <c r="W66" s="9" t="n"/>
+      <c r="X66" s="9" t="n"/>
+      <c r="Y66" s="9" t="n"/>
+      <c r="Z66" s="9" t="n"/>
+      <c r="AA66" s="9" t="n"/>
+      <c r="AB66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>R066</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Ai桌面宠物</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="n"/>
+      <c r="H67" s="9" t="n"/>
+      <c r="I67" s="9" t="n"/>
+      <c r="J67" s="9" t="n"/>
+      <c r="K67" s="9" t="n"/>
+      <c r="L67" s="9" t="n"/>
+      <c r="M67" s="9" t="n"/>
+      <c r="N67" s="9" t="n"/>
+      <c r="O67" s="9" t="n"/>
+      <c r="P67" s="9" t="n"/>
+      <c r="Q67" s="9" t="n"/>
+      <c r="R67" s="9" t="n"/>
+      <c r="S67" s="9" t="n"/>
+      <c r="T67" s="9" t="n"/>
+      <c r="U67" s="9" t="n"/>
+      <c r="V67" s="9" t="n"/>
+      <c r="W67" s="9" t="n"/>
+      <c r="X67" s="9" t="n"/>
+      <c r="Y67" s="9" t="n"/>
+      <c r="Z67" s="9" t="n"/>
+      <c r="AA67" s="9" t="n"/>
+      <c r="AB67" s="9" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>R067</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Ai桌面宠物</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="9" t="n"/>
+      <c r="G68" s="9" t="n"/>
+      <c r="H68" s="9" t="n"/>
+      <c r="I68" s="9" t="n"/>
+      <c r="J68" s="9" t="n"/>
+      <c r="K68" s="9" t="n"/>
+      <c r="L68" s="9" t="n"/>
+      <c r="M68" s="9" t="n"/>
+      <c r="N68" s="9" t="n"/>
+      <c r="O68" s="9" t="n"/>
+      <c r="P68" s="9" t="n"/>
+      <c r="Q68" s="9" t="n"/>
+      <c r="R68" s="9" t="n"/>
+      <c r="S68" s="9" t="n"/>
+      <c r="T68" s="9" t="n"/>
+      <c r="U68" s="9" t="n"/>
+      <c r="V68" s="9" t="n"/>
+      <c r="W68" s="9" t="n"/>
+      <c r="X68" s="9" t="n"/>
+      <c r="Y68" s="9" t="n"/>
+      <c r="Z68" s="9" t="n"/>
+      <c r="AA68" s="9" t="n"/>
+      <c r="AB68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>R068</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Ai桌面宠物</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="9" t="n"/>
+      <c r="G69" s="9" t="n"/>
+      <c r="H69" s="9" t="n"/>
+      <c r="I69" s="9" t="n"/>
+      <c r="J69" s="9" t="n"/>
+      <c r="K69" s="9" t="n"/>
+      <c r="L69" s="9" t="n"/>
+      <c r="M69" s="9" t="n"/>
+      <c r="N69" s="9" t="n"/>
+      <c r="O69" s="9" t="n"/>
+      <c r="P69" s="9" t="n"/>
+      <c r="Q69" s="9" t="n"/>
+      <c r="R69" s="9" t="n"/>
+      <c r="S69" s="9" t="n"/>
+      <c r="T69" s="9" t="n"/>
+      <c r="U69" s="9" t="n"/>
+      <c r="V69" s="9" t="n"/>
+      <c r="W69" s="9" t="n"/>
+      <c r="X69" s="9" t="n"/>
+      <c r="Y69" s="9" t="n"/>
+      <c r="Z69" s="9" t="n"/>
+      <c r="AA69" s="9" t="n"/>
+      <c r="AB69" s="9" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>R069</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Ai桌面宠物</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="n"/>
+      <c r="H70" s="9" t="n"/>
+      <c r="I70" s="9" t="n"/>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
+      <c r="L70" s="9" t="n"/>
+      <c r="M70" s="9" t="n"/>
+      <c r="N70" s="9" t="n"/>
+      <c r="O70" s="9" t="n"/>
+      <c r="P70" s="9" t="n"/>
+      <c r="Q70" s="9" t="n"/>
+      <c r="R70" s="9" t="n"/>
+      <c r="S70" s="9" t="n"/>
+      <c r="T70" s="9" t="n"/>
+      <c r="U70" s="9" t="n"/>
+      <c r="V70" s="9" t="n"/>
+      <c r="W70" s="9" t="n"/>
+      <c r="X70" s="9" t="n"/>
+      <c r="Y70" s="9" t="n"/>
+      <c r="Z70" s="9" t="n"/>
+      <c r="AA70" s="9" t="n"/>
+      <c r="AB70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>R070</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Ai桌面宠物</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="9" t="n"/>
+      <c r="G71" s="9" t="n"/>
+      <c r="H71" s="9" t="n"/>
+      <c r="I71" s="9" t="n"/>
+      <c r="J71" s="9" t="n"/>
+      <c r="K71" s="9" t="n"/>
+      <c r="L71" s="9" t="n"/>
+      <c r="M71" s="9" t="n"/>
+      <c r="N71" s="9" t="n"/>
+      <c r="O71" s="9" t="n"/>
+      <c r="P71" s="9" t="n"/>
+      <c r="Q71" s="9" t="n"/>
+      <c r="R71" s="9" t="n"/>
+      <c r="S71" s="9" t="n"/>
+      <c r="T71" s="9" t="n"/>
+      <c r="U71" s="9" t="n"/>
+      <c r="V71" s="9" t="n"/>
+      <c r="W71" s="9" t="n"/>
+      <c r="X71" s="9" t="n"/>
+      <c r="Y71" s="9" t="n"/>
+      <c r="Z71" s="9" t="n"/>
+      <c r="AA71" s="9" t="n"/>
+      <c r="AB71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>R071</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>角落里的艾果 Eggo</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="6" t="n"/>
+      <c r="H72" s="6" t="n"/>
+      <c r="I72" s="6" t="n"/>
+      <c r="J72" s="6" t="n"/>
+      <c r="K72" s="6" t="n"/>
+      <c r="L72" s="6" t="n"/>
+      <c r="M72" s="6" t="n"/>
+      <c r="N72" s="6" t="n"/>
+      <c r="O72" s="6" t="n"/>
+      <c r="P72" s="6" t="n"/>
+      <c r="Q72" s="6" t="n"/>
+      <c r="R72" s="6" t="n"/>
+      <c r="S72" s="6" t="n"/>
+      <c r="T72" s="6" t="n"/>
+      <c r="U72" s="6" t="n"/>
+      <c r="V72" s="6" t="n"/>
+      <c r="W72" s="6" t="n"/>
+      <c r="X72" s="6" t="n"/>
+      <c r="Y72" s="6" t="n"/>
+      <c r="Z72" s="6" t="n"/>
+      <c r="AA72" s="6" t="n"/>
+      <c r="AB72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>R072</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>角落里的艾果 Eggo</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="n"/>
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="6" t="n"/>
+      <c r="I73" s="6" t="n"/>
+      <c r="J73" s="6" t="n"/>
+      <c r="K73" s="6" t="n"/>
+      <c r="L73" s="6" t="n"/>
+      <c r="M73" s="6" t="n"/>
+      <c r="N73" s="6" t="n"/>
+      <c r="O73" s="6" t="n"/>
+      <c r="P73" s="6" t="n"/>
+      <c r="Q73" s="6" t="n"/>
+      <c r="R73" s="6" t="n"/>
+      <c r="S73" s="6" t="n"/>
+      <c r="T73" s="6" t="n"/>
+      <c r="U73" s="6" t="n"/>
+      <c r="V73" s="6" t="n"/>
+      <c r="W73" s="6" t="n"/>
+      <c r="X73" s="6" t="n"/>
+      <c r="Y73" s="6" t="n"/>
+      <c r="Z73" s="6" t="n"/>
+      <c r="AA73" s="6" t="n"/>
+      <c r="AB73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>R073</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>角落里的艾果 Eggo</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="6" t="n"/>
+      <c r="I74" s="6" t="n"/>
+      <c r="J74" s="6" t="n"/>
+      <c r="K74" s="6" t="n"/>
+      <c r="L74" s="6" t="n"/>
+      <c r="M74" s="6" t="n"/>
+      <c r="N74" s="6" t="n"/>
+      <c r="O74" s="6" t="n"/>
+      <c r="P74" s="6" t="n"/>
+      <c r="Q74" s="6" t="n"/>
+      <c r="R74" s="6" t="n"/>
+      <c r="S74" s="6" t="n"/>
+      <c r="T74" s="6" t="n"/>
+      <c r="U74" s="6" t="n"/>
+      <c r="V74" s="6" t="n"/>
+      <c r="W74" s="6" t="n"/>
+      <c r="X74" s="6" t="n"/>
+      <c r="Y74" s="6" t="n"/>
+      <c r="Z74" s="6" t="n"/>
+      <c r="AA74" s="6" t="n"/>
+      <c r="AB74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>R074</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>角落里的艾果 Eggo</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="6" t="n"/>
+      <c r="I75" s="6" t="n"/>
+      <c r="J75" s="6" t="n"/>
+      <c r="K75" s="6" t="n"/>
+      <c r="L75" s="6" t="n"/>
+      <c r="M75" s="6" t="n"/>
+      <c r="N75" s="6" t="n"/>
+      <c r="O75" s="6" t="n"/>
+      <c r="P75" s="6" t="n"/>
+      <c r="Q75" s="6" t="n"/>
+      <c r="R75" s="6" t="n"/>
+      <c r="S75" s="6" t="n"/>
+      <c r="T75" s="6" t="n"/>
+      <c r="U75" s="6" t="n"/>
+      <c r="V75" s="6" t="n"/>
+      <c r="W75" s="6" t="n"/>
+      <c r="X75" s="6" t="n"/>
+      <c r="Y75" s="6" t="n"/>
+      <c r="Z75" s="6" t="n"/>
+      <c r="AA75" s="6" t="n"/>
+      <c r="AB75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>R075</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>角落里的艾果 Eggo</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="6" t="n"/>
+      <c r="I76" s="6" t="n"/>
+      <c r="J76" s="6" t="n"/>
+      <c r="K76" s="6" t="n"/>
+      <c r="L76" s="6" t="n"/>
+      <c r="M76" s="6" t="n"/>
+      <c r="N76" s="6" t="n"/>
+      <c r="O76" s="6" t="n"/>
+      <c r="P76" s="6" t="n"/>
+      <c r="Q76" s="6" t="n"/>
+      <c r="R76" s="6" t="n"/>
+      <c r="S76" s="6" t="n"/>
+      <c r="T76" s="6" t="n"/>
+      <c r="U76" s="6" t="n"/>
+      <c r="V76" s="6" t="n"/>
+      <c r="W76" s="6" t="n"/>
+      <c r="X76" s="6" t="n"/>
+      <c r="Y76" s="6" t="n"/>
+      <c r="Z76" s="6" t="n"/>
+      <c r="AA76" s="6" t="n"/>
+      <c r="AB76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>R076</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>角落里的艾果 Eggo</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="n"/>
+      <c r="G77" s="6" t="n"/>
+      <c r="H77" s="6" t="n"/>
+      <c r="I77" s="6" t="n"/>
+      <c r="J77" s="6" t="n"/>
+      <c r="K77" s="6" t="n"/>
+      <c r="L77" s="6" t="n"/>
+      <c r="M77" s="6" t="n"/>
+      <c r="N77" s="6" t="n"/>
+      <c r="O77" s="6" t="n"/>
+      <c r="P77" s="6" t="n"/>
+      <c r="Q77" s="6" t="n"/>
+      <c r="R77" s="6" t="n"/>
+      <c r="S77" s="6" t="n"/>
+      <c r="T77" s="6" t="n"/>
+      <c r="U77" s="6" t="n"/>
+      <c r="V77" s="6" t="n"/>
+      <c r="W77" s="6" t="n"/>
+      <c r="X77" s="6" t="n"/>
+      <c r="Y77" s="6" t="n"/>
+      <c r="Z77" s="6" t="n"/>
+      <c r="AA77" s="6" t="n"/>
+      <c r="AB77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>R077</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>角落里的艾果 Eggo</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="n"/>
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="6" t="n"/>
+      <c r="I78" s="6" t="n"/>
+      <c r="J78" s="6" t="n"/>
+      <c r="K78" s="6" t="n"/>
+      <c r="L78" s="6" t="n"/>
+      <c r="M78" s="6" t="n"/>
+      <c r="N78" s="6" t="n"/>
+      <c r="O78" s="6" t="n"/>
+      <c r="P78" s="6" t="n"/>
+      <c r="Q78" s="6" t="n"/>
+      <c r="R78" s="6" t="n"/>
+      <c r="S78" s="6" t="n"/>
+      <c r="T78" s="6" t="n"/>
+      <c r="U78" s="6" t="n"/>
+      <c r="V78" s="6" t="n"/>
+      <c r="W78" s="6" t="n"/>
+      <c r="X78" s="6" t="n"/>
+      <c r="Y78" s="6" t="n"/>
+      <c r="Z78" s="6" t="n"/>
+      <c r="AA78" s="6" t="n"/>
+      <c r="AB78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>R078</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Molili Ai Friends: Ai 桌面宠物</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="9" t="n"/>
+      <c r="H79" s="9" t="n"/>
+      <c r="I79" s="9" t="n"/>
+      <c r="J79" s="9" t="n"/>
+      <c r="K79" s="9" t="n"/>
+      <c r="L79" s="9" t="n"/>
+      <c r="M79" s="9" t="n"/>
+      <c r="N79" s="9" t="n"/>
+      <c r="O79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
+      <c r="Q79" s="9" t="n"/>
+      <c r="R79" s="9" t="n"/>
+      <c r="S79" s="9" t="n"/>
+      <c r="T79" s="9" t="n"/>
+      <c r="U79" s="9" t="n"/>
+      <c r="V79" s="9" t="n"/>
+      <c r="W79" s="9" t="n"/>
+      <c r="X79" s="9" t="n"/>
+      <c r="Y79" s="9" t="n"/>
+      <c r="Z79" s="9" t="n"/>
+      <c r="AA79" s="9" t="n"/>
+      <c r="AB79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>R079</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Molili Ai Friends: Ai 桌面宠物</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="9" t="n"/>
+      <c r="G80" s="9" t="n"/>
+      <c r="H80" s="9" t="n"/>
+      <c r="I80" s="9" t="n"/>
+      <c r="J80" s="9" t="n"/>
+      <c r="K80" s="9" t="n"/>
+      <c r="L80" s="9" t="n"/>
+      <c r="M80" s="9" t="n"/>
+      <c r="N80" s="9" t="n"/>
+      <c r="O80" s="9" t="n"/>
+      <c r="P80" s="9" t="n"/>
+      <c r="Q80" s="9" t="n"/>
+      <c r="R80" s="9" t="n"/>
+      <c r="S80" s="9" t="n"/>
+      <c r="T80" s="9" t="n"/>
+      <c r="U80" s="9" t="n"/>
+      <c r="V80" s="9" t="n"/>
+      <c r="W80" s="9" t="n"/>
+      <c r="X80" s="9" t="n"/>
+      <c r="Y80" s="9" t="n"/>
+      <c r="Z80" s="9" t="n"/>
+      <c r="AA80" s="9" t="n"/>
+      <c r="AB80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>R080</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Molili Ai Friends: Ai 桌面宠物</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="9" t="n"/>
+      <c r="H81" s="9" t="n"/>
+      <c r="I81" s="9" t="n"/>
+      <c r="J81" s="9" t="n"/>
+      <c r="K81" s="9" t="n"/>
+      <c r="L81" s="9" t="n"/>
+      <c r="M81" s="9" t="n"/>
+      <c r="N81" s="9" t="n"/>
+      <c r="O81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
+      <c r="Q81" s="9" t="n"/>
+      <c r="R81" s="9" t="n"/>
+      <c r="S81" s="9" t="n"/>
+      <c r="T81" s="9" t="n"/>
+      <c r="U81" s="9" t="n"/>
+      <c r="V81" s="9" t="n"/>
+      <c r="W81" s="9" t="n"/>
+      <c r="X81" s="9" t="n"/>
+      <c r="Y81" s="9" t="n"/>
+      <c r="Z81" s="9" t="n"/>
+      <c r="AA81" s="9" t="n"/>
+      <c r="AB81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>R081</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Molili Ai Friends: Ai 桌面宠物</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="9" t="n"/>
+      <c r="G82" s="9" t="n"/>
+      <c r="H82" s="9" t="n"/>
+      <c r="I82" s="9" t="n"/>
+      <c r="J82" s="9" t="n"/>
+      <c r="K82" s="9" t="n"/>
+      <c r="L82" s="9" t="n"/>
+      <c r="M82" s="9" t="n"/>
+      <c r="N82" s="9" t="n"/>
+      <c r="O82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="Q82" s="9" t="n"/>
+      <c r="R82" s="9" t="n"/>
+      <c r="S82" s="9" t="n"/>
+      <c r="T82" s="9" t="n"/>
+      <c r="U82" s="9" t="n"/>
+      <c r="V82" s="9" t="n"/>
+      <c r="W82" s="9" t="n"/>
+      <c r="X82" s="9" t="n"/>
+      <c r="Y82" s="9" t="n"/>
+      <c r="Z82" s="9" t="n"/>
+      <c r="AA82" s="9" t="n"/>
+      <c r="AB82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>R082</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>Molili Ai Friends: Ai 桌面宠物</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="9" t="n"/>
+      <c r="H83" s="9" t="n"/>
+      <c r="I83" s="9" t="n"/>
+      <c r="J83" s="9" t="n"/>
+      <c r="K83" s="9" t="n"/>
+      <c r="L83" s="9" t="n"/>
+      <c r="M83" s="9" t="n"/>
+      <c r="N83" s="9" t="n"/>
+      <c r="O83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
+      <c r="Q83" s="9" t="n"/>
+      <c r="R83" s="9" t="n"/>
+      <c r="S83" s="9" t="n"/>
+      <c r="T83" s="9" t="n"/>
+      <c r="U83" s="9" t="n"/>
+      <c r="V83" s="9" t="n"/>
+      <c r="W83" s="9" t="n"/>
+      <c r="X83" s="9" t="n"/>
+      <c r="Y83" s="9" t="n"/>
+      <c r="Z83" s="9" t="n"/>
+      <c r="AA83" s="9" t="n"/>
+      <c r="AB83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>R083</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Molili Ai Friends: Ai 桌面宠物</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="9" t="n"/>
+      <c r="H84" s="9" t="n"/>
+      <c r="I84" s="9" t="n"/>
+      <c r="J84" s="9" t="n"/>
+      <c r="K84" s="9" t="n"/>
+      <c r="L84" s="9" t="n"/>
+      <c r="M84" s="9" t="n"/>
+      <c r="N84" s="9" t="n"/>
+      <c r="O84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
+      <c r="Q84" s="9" t="n"/>
+      <c r="R84" s="9" t="n"/>
+      <c r="S84" s="9" t="n"/>
+      <c r="T84" s="9" t="n"/>
+      <c r="U84" s="9" t="n"/>
+      <c r="V84" s="9" t="n"/>
+      <c r="W84" s="9" t="n"/>
+      <c r="X84" s="9" t="n"/>
+      <c r="Y84" s="9" t="n"/>
+      <c r="Z84" s="9" t="n"/>
+      <c r="AA84" s="9" t="n"/>
+      <c r="AB84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>R084</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Molili Ai Friends: Ai 桌面宠物</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="9" t="n"/>
+      <c r="I85" s="9" t="n"/>
+      <c r="J85" s="9" t="n"/>
+      <c r="K85" s="9" t="n"/>
+      <c r="L85" s="9" t="n"/>
+      <c r="M85" s="9" t="n"/>
+      <c r="N85" s="9" t="n"/>
+      <c r="O85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="Q85" s="9" t="n"/>
+      <c r="R85" s="9" t="n"/>
+      <c r="S85" s="9" t="n"/>
+      <c r="T85" s="9" t="n"/>
+      <c r="U85" s="9" t="n"/>
+      <c r="V85" s="9" t="n"/>
+      <c r="W85" s="9" t="n"/>
+      <c r="X85" s="9" t="n"/>
+      <c r="Y85" s="9" t="n"/>
+      <c r="Z85" s="9" t="n"/>
+      <c r="AA85" s="9" t="n"/>
+      <c r="AB85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>R085</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>猫娘计划 - N.E.K.O</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>系统基线</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="9" t="n"/>
+      <c r="H86" s="9" t="n"/>
+      <c r="I86" s="9" t="n"/>
+      <c r="J86" s="9" t="n"/>
+      <c r="K86" s="9" t="n"/>
+      <c r="L86" s="9" t="n"/>
+      <c r="M86" s="9" t="n"/>
+      <c r="N86" s="9" t="n"/>
+      <c r="O86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="Q86" s="9" t="n"/>
+      <c r="R86" s="9" t="n"/>
+      <c r="S86" s="9" t="n"/>
+      <c r="T86" s="9" t="n"/>
+      <c r="U86" s="9" t="n"/>
+      <c r="V86" s="9" t="n"/>
+      <c r="W86" s="9" t="n"/>
+      <c r="X86" s="9" t="n"/>
+      <c r="Y86" s="9" t="n"/>
+      <c r="Z86" s="9" t="n"/>
+      <c r="AA86" s="9" t="n"/>
+      <c r="AB86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>R086</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>猫娘计划 - N.E.K.O</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>启动峰值</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="9" t="n"/>
+      <c r="H87" s="9" t="n"/>
+      <c r="I87" s="9" t="n"/>
+      <c r="J87" s="9" t="n"/>
+      <c r="K87" s="9" t="n"/>
+      <c r="L87" s="9" t="n"/>
+      <c r="M87" s="9" t="n"/>
+      <c r="N87" s="9" t="n"/>
+      <c r="O87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
+      <c r="Q87" s="9" t="n"/>
+      <c r="R87" s="9" t="n"/>
+      <c r="S87" s="9" t="n"/>
+      <c r="T87" s="9" t="n"/>
+      <c r="U87" s="9" t="n"/>
+      <c r="V87" s="9" t="n"/>
+      <c r="W87" s="9" t="n"/>
+      <c r="X87" s="9" t="n"/>
+      <c r="Y87" s="9" t="n"/>
+      <c r="Z87" s="9" t="n"/>
+      <c r="AA87" s="9" t="n"/>
+      <c r="AB87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>R087</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>猫娘计划 - N.E.K.O</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>空闲常驻</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="9" t="n"/>
+      <c r="H88" s="9" t="n"/>
+      <c r="I88" s="9" t="n"/>
+      <c r="J88" s="9" t="n"/>
+      <c r="K88" s="9" t="n"/>
+      <c r="L88" s="9" t="n"/>
+      <c r="M88" s="9" t="n"/>
+      <c r="N88" s="9" t="n"/>
+      <c r="O88" s="9" t="n"/>
+      <c r="P88" s="9" t="n"/>
+      <c r="Q88" s="9" t="n"/>
+      <c r="R88" s="9" t="n"/>
+      <c r="S88" s="9" t="n"/>
+      <c r="T88" s="9" t="n"/>
+      <c r="U88" s="9" t="n"/>
+      <c r="V88" s="9" t="n"/>
+      <c r="W88" s="9" t="n"/>
+      <c r="X88" s="9" t="n"/>
+      <c r="Y88" s="9" t="n"/>
+      <c r="Z88" s="9" t="n"/>
+      <c r="AA88" s="9" t="n"/>
+      <c r="AB88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>R088</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>猫娘计划 - N.E.K.O</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>基础交互</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
+      <c r="H89" s="9" t="n"/>
+      <c r="I89" s="9" t="n"/>
+      <c r="J89" s="9" t="n"/>
+      <c r="K89" s="9" t="n"/>
+      <c r="L89" s="9" t="n"/>
+      <c r="M89" s="9" t="n"/>
+      <c r="N89" s="9" t="n"/>
+      <c r="O89" s="9" t="n"/>
+      <c r="P89" s="9" t="n"/>
+      <c r="Q89" s="9" t="n"/>
+      <c r="R89" s="9" t="n"/>
+      <c r="S89" s="9" t="n"/>
+      <c r="T89" s="9" t="n"/>
+      <c r="U89" s="9" t="n"/>
+      <c r="V89" s="9" t="n"/>
+      <c r="W89" s="9" t="n"/>
+      <c r="X89" s="9" t="n"/>
+      <c r="Y89" s="9" t="n"/>
+      <c r="Z89" s="9" t="n"/>
+      <c r="AA89" s="9" t="n"/>
+      <c r="AB89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>R089</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>猫娘计划 - N.E.K.O</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>功能开启</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="9" t="n"/>
+      <c r="H90" s="9" t="n"/>
+      <c r="I90" s="9" t="n"/>
+      <c r="J90" s="9" t="n"/>
+      <c r="K90" s="9" t="n"/>
+      <c r="L90" s="9" t="n"/>
+      <c r="M90" s="9" t="n"/>
+      <c r="N90" s="9" t="n"/>
+      <c r="O90" s="9" t="n"/>
+      <c r="P90" s="9" t="n"/>
+      <c r="Q90" s="9" t="n"/>
+      <c r="R90" s="9" t="n"/>
+      <c r="S90" s="9" t="n"/>
+      <c r="T90" s="9" t="n"/>
+      <c r="U90" s="9" t="n"/>
+      <c r="V90" s="9" t="n"/>
+      <c r="W90" s="9" t="n"/>
+      <c r="X90" s="9" t="n"/>
+      <c r="Y90" s="9" t="n"/>
+      <c r="Z90" s="9" t="n"/>
+      <c r="AA90" s="9" t="n"/>
+      <c r="AB90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>R090</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>猫娘计划 - N.E.K.O</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>长时间稳定</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="9" t="n"/>
+      <c r="I91" s="9" t="n"/>
+      <c r="J91" s="9" t="n"/>
+      <c r="K91" s="9" t="n"/>
+      <c r="L91" s="9" t="n"/>
+      <c r="M91" s="9" t="n"/>
+      <c r="N91" s="9" t="n"/>
+      <c r="O91" s="9" t="n"/>
+      <c r="P91" s="9" t="n"/>
+      <c r="Q91" s="9" t="n"/>
+      <c r="R91" s="9" t="n"/>
+      <c r="S91" s="9" t="n"/>
+      <c r="T91" s="9" t="n"/>
+      <c r="U91" s="9" t="n"/>
+      <c r="V91" s="9" t="n"/>
+      <c r="W91" s="9" t="n"/>
+      <c r="X91" s="9" t="n"/>
+      <c r="Y91" s="9" t="n"/>
+      <c r="Z91" s="9" t="n"/>
+      <c r="AA91" s="9" t="n"/>
+      <c r="AB91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>R091</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>猫娘计划 - N.E.K.O</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>游戏影响</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="9" t="n"/>
+      <c r="I92" s="9" t="n"/>
+      <c r="J92" s="9" t="n"/>
+      <c r="K92" s="9" t="n"/>
+      <c r="L92" s="9" t="n"/>
+      <c r="M92" s="9" t="n"/>
+      <c r="N92" s="9" t="n"/>
+      <c r="O92" s="9" t="n"/>
+      <c r="P92" s="9" t="n"/>
+      <c r="Q92" s="9" t="n"/>
+      <c r="R92" s="9" t="n"/>
+      <c r="S92" s="9" t="n"/>
+      <c r="T92" s="9" t="n"/>
+      <c r="U92" s="9" t="n"/>
+      <c r="V92" s="9" t="n"/>
+      <c r="W92" s="9" t="n"/>
+      <c r="X92" s="9" t="n"/>
+      <c r="Y92" s="9" t="n"/>
+      <c r="Z92" s="9" t="n"/>
+      <c r="AA92" s="9" t="n"/>
+      <c r="AB92" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AB22"/>
@@ -3702,2204 +7759,1244 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2">
-        <f>IF(产品清单!A2="","",产品清单!A2)</f>
-        <v/>
-      </c>
-      <c r="B2" s="2">
-        <f>IF(产品清单!B2="","",产品清单!B2)</f>
-        <v/>
-      </c>
-      <c r="C2" s="2">
-        <f>IF(产品清单!C2="","",产品清单!C2)</f>
-        <v/>
-      </c>
-      <c r="D2" s="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>BongoCat</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>GitHub Release/本地安装</t>
+        </is>
+      </c>
+      <c r="D2" s="11">
         <f>IF($A2="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A2,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="11">
         <f>IF($A2="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A2,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="11">
         <f>IF($A2="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A2),""))</f>
         <v/>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2">
+      <c r="G2" s="11" t="inlineStr"/>
+      <c r="H2" s="11" t="inlineStr"/>
+      <c r="I2" s="11" t="inlineStr"/>
+      <c r="J2" s="11">
         <f>IF($A2="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A2),""))</f>
         <v/>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2">
+      <c r="K2" s="11" t="inlineStr"/>
+      <c r="L2" s="11" t="inlineStr"/>
+      <c r="M2" s="11">
         <f>IF($A2="","",IFERROR(ROUND(AVERAGE(I2:L2),1),""))</f>
         <v/>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="11">
         <f>IF(M2="","",IF(M2&gt;=4.2,"推荐",IF(M2&gt;=3.4,"可接受",IF(M2&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" s="11" t="inlineStr"/>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="2">
-        <f>IF(产品清单!A3="","",产品清单!A3)</f>
-        <v/>
-      </c>
-      <c r="B3" s="2">
-        <f>IF(产品清单!B3="","",产品清单!B3)</f>
-        <v/>
-      </c>
-      <c r="C3" s="2">
-        <f>IF(产品清单!C3="","",产品清单!C3)</f>
-        <v/>
-      </c>
-      <c r="D3" s="2">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Desktop Mate</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D3" s="12">
         <f>IF($A3="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A3,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="12">
         <f>IF($A3="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A3,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="12">
         <f>IF($A3="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A3),""))</f>
         <v/>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2">
+      <c r="G3" s="12" t="inlineStr"/>
+      <c r="H3" s="12" t="inlineStr"/>
+      <c r="I3" s="12" t="inlineStr"/>
+      <c r="J3" s="12">
         <f>IF($A3="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A3),""))</f>
         <v/>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2">
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr"/>
+      <c r="M3" s="12">
         <f>IF($A3="","",IFERROR(ROUND(AVERAGE(I3:L3),1),""))</f>
         <v/>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="12">
         <f>IF(M3="","",IF(M3&gt;=4.2,"推荐",IF(M3&gt;=3.4,"可接受",IF(M3&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O3" s="2" t="inlineStr"/>
+      <c r="O3" s="12" t="inlineStr"/>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="2">
-        <f>IF(产品清单!A4="","",产品清单!A4)</f>
-        <v/>
-      </c>
-      <c r="B4" s="2">
-        <f>IF(产品清单!B4="","",产品清单!B4)</f>
-        <v/>
-      </c>
-      <c r="C4" s="2">
-        <f>IF(产品清单!C4="","",产品清单!C4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="2">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>VPet-Simulator</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D4" s="11">
         <f>IF($A4="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A4,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="11">
         <f>IF($A4="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A4,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="11">
         <f>IF($A4="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A4),""))</f>
         <v/>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2">
+      <c r="G4" s="11" t="inlineStr"/>
+      <c r="H4" s="11" t="inlineStr"/>
+      <c r="I4" s="11" t="inlineStr"/>
+      <c r="J4" s="11">
         <f>IF($A4="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A4),""))</f>
         <v/>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2">
+      <c r="K4" s="11" t="inlineStr"/>
+      <c r="L4" s="11" t="inlineStr"/>
+      <c r="M4" s="11">
         <f>IF($A4="","",IFERROR(ROUND(AVERAGE(I4:L4),1),""))</f>
         <v/>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="11">
         <f>IF(M4="","",IF(M4&gt;=4.2,"推荐",IF(M4&gt;=3.4,"可接受",IF(M4&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="2">
-        <f>IF(产品清单!A5="","",产品清单!A5)</f>
-        <v/>
-      </c>
-      <c r="B5" s="2">
-        <f>IF(产品清单!B5="","",产品清单!B5)</f>
-        <v/>
-      </c>
-      <c r="C5" s="2">
-        <f>IF(产品清单!C5="","",产品清单!C5)</f>
-        <v/>
-      </c>
-      <c r="D5" s="2">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Desktop Goose</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>itch.io</t>
+        </is>
+      </c>
+      <c r="D5" s="13">
         <f>IF($A5="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A5,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="13">
         <f>IF($A5="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A5,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="13">
         <f>IF($A5="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A5),""))</f>
         <v/>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2">
+      <c r="G5" s="13" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr"/>
+      <c r="I5" s="13" t="inlineStr"/>
+      <c r="J5" s="13">
         <f>IF($A5="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A5),""))</f>
         <v/>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2">
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
+      <c r="M5" s="13">
         <f>IF($A5="","",IFERROR(ROUND(AVERAGE(I5:L5),1),""))</f>
         <v/>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="13">
         <f>IF(M5="","",IF(M5&gt;=4.2,"推荐",IF(M5&gt;=3.4,"可接受",IF(M5&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O5" s="2" t="inlineStr"/>
+      <c r="O5" s="13" t="inlineStr"/>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="2">
-        <f>IF(产品清单!A6="","",产品清单!A6)</f>
-        <v/>
-      </c>
-      <c r="B6" s="2">
-        <f>IF(产品清单!B6="","",产品清单!B6)</f>
-        <v/>
-      </c>
-      <c r="C6" s="2">
-        <f>IF(产品清单!C6="","",产品清单!C6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="2">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Ai Vpet</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D6" s="14">
         <f>IF($A6="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A6,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="14">
         <f>IF($A6="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A6,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="14">
         <f>IF($A6="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A6),""))</f>
         <v/>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2">
+      <c r="G6" s="14" t="inlineStr"/>
+      <c r="H6" s="14" t="inlineStr"/>
+      <c r="I6" s="14" t="inlineStr"/>
+      <c r="J6" s="14">
         <f>IF($A6="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A6),""))</f>
         <v/>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2">
+      <c r="K6" s="14" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
+      <c r="M6" s="14">
         <f>IF($A6="","",IFERROR(ROUND(AVERAGE(I6:L6),1),""))</f>
         <v/>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="14">
         <f>IF(M6="","",IF(M6&gt;=4.2,"推荐",IF(M6&gt;=3.4,"可接受",IF(M6&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="O6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="2">
-        <f>IF(产品清单!A7="","",产品清单!A7)</f>
-        <v/>
-      </c>
-      <c r="B7" s="2">
-        <f>IF(产品清单!B7="","",产品清单!B7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="2">
-        <f>IF(产品清单!C7="","",产品清单!C7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="2">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Tiny Pasture</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D7" s="11">
         <f>IF($A7="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A7,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="11">
         <f>IF($A7="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A7,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="11">
         <f>IF($A7="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A7),""))</f>
         <v/>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2">
+      <c r="G7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr"/>
+      <c r="J7" s="11">
         <f>IF($A7="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A7),""))</f>
         <v/>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2">
+      <c r="K7" s="11" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr"/>
+      <c r="M7" s="11">
         <f>IF($A7="","",IFERROR(ROUND(AVERAGE(I7:L7),1),""))</f>
         <v/>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="11">
         <f>IF(M7="","",IF(M7&gt;=4.2,"推荐",IF(M7&gt;=3.4,"可接受",IF(M7&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O7" s="2" t="inlineStr"/>
+      <c r="O7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="2">
-        <f>IF(产品清单!A8="","",产品清单!A8)</f>
-        <v/>
-      </c>
-      <c r="B8" s="2">
-        <f>IF(产品清单!B8="","",产品清单!B8)</f>
-        <v/>
-      </c>
-      <c r="C8" s="2">
-        <f>IF(产品清单!C8="","",产品清单!C8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="2">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Pocket Waifu:Desktop Pet</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D8" s="12">
         <f>IF($A8="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A8,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="12">
         <f>IF($A8="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A8,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="12">
         <f>IF($A8="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A8),""))</f>
         <v/>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2">
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="12" t="inlineStr"/>
+      <c r="I8" s="12" t="inlineStr"/>
+      <c r="J8" s="12">
         <f>IF($A8="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A8),""))</f>
         <v/>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2">
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="12" t="inlineStr"/>
+      <c r="M8" s="12">
         <f>IF($A8="","",IFERROR(ROUND(AVERAGE(I8:L8),1),""))</f>
         <v/>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="12">
         <f>IF(M8="","",IF(M8&gt;=4.2,"推荐",IF(M8&gt;=3.4,"可接受",IF(M8&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="2">
-        <f>IF(产品清单!A9="","",产品清单!A9)</f>
-        <v/>
-      </c>
-      <c r="B9" s="2">
-        <f>IF(产品清单!B9="","",产品清单!B9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="2">
-        <f>IF(产品清单!C9="","",产品清单!C9)</f>
-        <v/>
-      </c>
-      <c r="D9" s="2">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Rusty's Retirement</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D9" s="15">
         <f>IF($A9="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A9,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="15">
         <f>IF($A9="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A9,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="15">
         <f>IF($A9="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A9),""))</f>
         <v/>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2">
+      <c r="G9" s="15" t="inlineStr"/>
+      <c r="H9" s="15" t="inlineStr"/>
+      <c r="I9" s="15" t="inlineStr"/>
+      <c r="J9" s="15">
         <f>IF($A9="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A9),""))</f>
         <v/>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2">
+      <c r="K9" s="15" t="inlineStr"/>
+      <c r="L9" s="15" t="inlineStr"/>
+      <c r="M9" s="15">
         <f>IF($A9="","",IFERROR(ROUND(AVERAGE(I9:L9),1),""))</f>
         <v/>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="15">
         <f>IF(M9="","",IF(M9&gt;=4.2,"推荐",IF(M9&gt;=3.4,"可接受",IF(M9&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O9" s="2" t="inlineStr"/>
+      <c r="O9" s="15" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="2">
-        <f>IF(产品清单!A10="","",产品清单!A10)</f>
-        <v/>
-      </c>
-      <c r="B10" s="2">
-        <f>IF(产品清单!B10="","",产品清单!B10)</f>
-        <v/>
-      </c>
-      <c r="C10" s="2">
-        <f>IF(产品清单!C10="","",产品清单!C10)</f>
-        <v/>
-      </c>
-      <c r="D10" s="2">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>MateEngine</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D10" s="12">
         <f>IF($A10="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A10,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="12">
         <f>IF($A10="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A10,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="12">
         <f>IF($A10="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A10),""))</f>
         <v/>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2">
+      <c r="G10" s="12" t="inlineStr"/>
+      <c r="H10" s="12" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr"/>
+      <c r="J10" s="12">
         <f>IF($A10="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A10),""))</f>
         <v/>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2">
+      <c r="K10" s="12" t="inlineStr"/>
+      <c r="L10" s="12" t="inlineStr"/>
+      <c r="M10" s="12">
         <f>IF($A10="","",IFERROR(ROUND(AVERAGE(I10:L10),1),""))</f>
         <v/>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="12">
         <f>IF(M10="","",IF(M10&gt;=4.2,"推荐",IF(M10&gt;=3.4,"可接受",IF(M10&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="2">
-        <f>IF(产品清单!A11="","",产品清单!A11)</f>
-        <v/>
-      </c>
-      <c r="B11" s="2">
-        <f>IF(产品清单!B11="","",产品清单!B11)</f>
-        <v/>
-      </c>
-      <c r="C11" s="2">
-        <f>IF(产品清单!C11="","",产品清单!C11)</f>
-        <v/>
-      </c>
-      <c r="D11" s="2">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Ai桌面宠物</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D11" s="14">
         <f>IF($A11="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A11,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="14">
         <f>IF($A11="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A11,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="14">
         <f>IF($A11="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A11),""))</f>
         <v/>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2">
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
+      <c r="J11" s="14">
         <f>IF($A11="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A11),""))</f>
         <v/>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2">
+      <c r="K11" s="14" t="inlineStr"/>
+      <c r="L11" s="14" t="inlineStr"/>
+      <c r="M11" s="14">
         <f>IF($A11="","",IFERROR(ROUND(AVERAGE(I11:L11),1),""))</f>
         <v/>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="14">
         <f>IF(M11="","",IF(M11&gt;=4.2,"推荐",IF(M11&gt;=3.4,"可接受",IF(M11&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
+      <c r="O11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="2">
-        <f>IF(产品清单!A12="","",产品清单!A12)</f>
-        <v/>
-      </c>
-      <c r="B12" s="2">
-        <f>IF(产品清单!B12="","",产品清单!B12)</f>
-        <v/>
-      </c>
-      <c r="C12" s="2">
-        <f>IF(产品清单!C12="","",产品清单!C12)</f>
-        <v/>
-      </c>
-      <c r="D12" s="2">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>角落里的艾果 Eggo</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D12" s="11">
         <f>IF($A12="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A12,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="11">
         <f>IF($A12="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A12,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="11">
         <f>IF($A12="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A12),""))</f>
         <v/>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2">
+      <c r="G12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="11" t="inlineStr"/>
+      <c r="J12" s="11">
         <f>IF($A12="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A12),""))</f>
         <v/>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2">
+      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr"/>
+      <c r="M12" s="11">
         <f>IF($A12="","",IFERROR(ROUND(AVERAGE(I12:L12),1),""))</f>
         <v/>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="11">
         <f>IF(M12="","",IF(M12&gt;=4.2,"推荐",IF(M12&gt;=3.4,"可接受",IF(M12&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="2">
-        <f>IF(产品清单!A13="","",产品清单!A13)</f>
-        <v/>
-      </c>
-      <c r="B13" s="2">
-        <f>IF(产品清单!B13="","",产品清单!B13)</f>
-        <v/>
-      </c>
-      <c r="C13" s="2">
-        <f>IF(产品清单!C13="","",产品清单!C13)</f>
-        <v/>
-      </c>
-      <c r="D13" s="2">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Molili Ai Friends: Ai 桌面宠物</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D13" s="14">
         <f>IF($A13="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A13,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="14">
         <f>IF($A13="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A13,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="14">
         <f>IF($A13="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A13),""))</f>
         <v/>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2">
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr"/>
+      <c r="J13" s="14">
         <f>IF($A13="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A13),""))</f>
         <v/>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2">
+      <c r="K13" s="14" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr"/>
+      <c r="M13" s="14">
         <f>IF($A13="","",IFERROR(ROUND(AVERAGE(I13:L13),1),""))</f>
         <v/>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="14">
         <f>IF(M13="","",IF(M13&gt;=4.2,"推荐",IF(M13&gt;=3.4,"可接受",IF(M13&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O13" s="2" t="inlineStr"/>
+      <c r="O13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="2">
-        <f>IF(产品清单!A14="","",产品清单!A14)</f>
-        <v/>
-      </c>
-      <c r="B14" s="2">
-        <f>IF(产品清单!B14="","",产品清单!B14)</f>
-        <v/>
-      </c>
-      <c r="C14" s="2">
-        <f>IF(产品清单!C14="","",产品清单!C14)</f>
-        <v/>
-      </c>
-      <c r="D14" s="2">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>猫娘计划 - N.E.K.O</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Steam</t>
+        </is>
+      </c>
+      <c r="D14" s="14">
         <f>IF($A14="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A14,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="14">
         <f>IF($A14="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A14,场景记录!D:D,"空闲常驻"),""))</f>
         <v/>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="14">
         <f>IF($A14="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A14),""))</f>
         <v/>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2">
+      <c r="G14" s="14" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr"/>
+      <c r="I14" s="14" t="inlineStr"/>
+      <c r="J14" s="14">
         <f>IF($A14="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A14),""))</f>
         <v/>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2">
+      <c r="K14" s="14" t="inlineStr"/>
+      <c r="L14" s="14" t="inlineStr"/>
+      <c r="M14" s="14">
         <f>IF($A14="","",IFERROR(ROUND(AVERAGE(I14:L14),1),""))</f>
         <v/>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="14">
         <f>IF(M14="","",IF(M14&gt;=4.2,"推荐",IF(M14&gt;=3.4,"可接受",IF(M14&gt;=2.6,"谨慎","不推荐"))))</f>
         <v/>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
+      <c r="O14" s="14" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="2">
-        <f>IF(产品清单!A15="","",产品清单!A15)</f>
-        <v/>
-      </c>
-      <c r="B15" s="2">
-        <f>IF(产品清单!B15="","",产品清单!B15)</f>
-        <v/>
-      </c>
-      <c r="C15" s="2">
-        <f>IF(产品清单!C15="","",产品清单!C15)</f>
-        <v/>
-      </c>
-      <c r="D15" s="2">
-        <f>IF($A15="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A15,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E15" s="2">
-        <f>IF($A15="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A15,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F15" s="2">
-        <f>IF($A15="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A15),""))</f>
-        <v/>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2">
-        <f>IF($A15="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A15),""))</f>
-        <v/>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2">
-        <f>IF($A15="","",IFERROR(ROUND(AVERAGE(I15:L15),1),""))</f>
-        <v/>
-      </c>
-      <c r="N15" s="2">
-        <f>IF(M15="","",IF(M15&gt;=4.2,"推荐",IF(M15&gt;=3.4,"可接受",IF(M15&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="2">
-        <f>IF(产品清单!A16="","",产品清单!A16)</f>
-        <v/>
-      </c>
-      <c r="B16" s="2">
-        <f>IF(产品清单!B16="","",产品清单!B16)</f>
-        <v/>
-      </c>
-      <c r="C16" s="2">
-        <f>IF(产品清单!C16="","",产品清单!C16)</f>
-        <v/>
-      </c>
-      <c r="D16" s="2">
-        <f>IF($A16="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A16,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E16" s="2">
-        <f>IF($A16="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A16,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F16" s="2">
-        <f>IF($A16="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A16),""))</f>
-        <v/>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2">
-        <f>IF($A16="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A16),""))</f>
-        <v/>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2">
-        <f>IF($A16="","",IFERROR(ROUND(AVERAGE(I16:L16),1),""))</f>
-        <v/>
-      </c>
-      <c r="N16" s="2">
-        <f>IF(M16="","",IF(M16&gt;=4.2,"推荐",IF(M16&gt;=3.4,"可接受",IF(M16&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="2">
-        <f>IF(产品清单!A17="","",产品清单!A17)</f>
-        <v/>
-      </c>
-      <c r="B17" s="2">
-        <f>IF(产品清单!B17="","",产品清单!B17)</f>
-        <v/>
-      </c>
-      <c r="C17" s="2">
-        <f>IF(产品清单!C17="","",产品清单!C17)</f>
-        <v/>
-      </c>
-      <c r="D17" s="2">
-        <f>IF($A17="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A17,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E17" s="2">
-        <f>IF($A17="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A17,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F17" s="2">
-        <f>IF($A17="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A17),""))</f>
-        <v/>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2">
-        <f>IF($A17="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A17),""))</f>
-        <v/>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2">
-        <f>IF($A17="","",IFERROR(ROUND(AVERAGE(I17:L17),1),""))</f>
-        <v/>
-      </c>
-      <c r="N17" s="2">
-        <f>IF(M17="","",IF(M17&gt;=4.2,"推荐",IF(M17&gt;=3.4,"可接受",IF(M17&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="2">
-        <f>IF(产品清单!A18="","",产品清单!A18)</f>
-        <v/>
-      </c>
-      <c r="B18" s="2">
-        <f>IF(产品清单!B18="","",产品清单!B18)</f>
-        <v/>
-      </c>
-      <c r="C18" s="2">
-        <f>IF(产品清单!C18="","",产品清单!C18)</f>
-        <v/>
-      </c>
-      <c r="D18" s="2">
-        <f>IF($A18="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A18,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E18" s="2">
-        <f>IF($A18="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A18,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F18" s="2">
-        <f>IF($A18="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A18),""))</f>
-        <v/>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2">
-        <f>IF($A18="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A18),""))</f>
-        <v/>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2">
-        <f>IF($A18="","",IFERROR(ROUND(AVERAGE(I18:L18),1),""))</f>
-        <v/>
-      </c>
-      <c r="N18" s="2">
-        <f>IF(M18="","",IF(M18&gt;=4.2,"推荐",IF(M18&gt;=3.4,"可接受",IF(M18&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="2">
-        <f>IF(产品清单!A19="","",产品清单!A19)</f>
-        <v/>
-      </c>
-      <c r="B19" s="2">
-        <f>IF(产品清单!B19="","",产品清单!B19)</f>
-        <v/>
-      </c>
-      <c r="C19" s="2">
-        <f>IF(产品清单!C19="","",产品清单!C19)</f>
-        <v/>
-      </c>
-      <c r="D19" s="2">
-        <f>IF($A19="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A19,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E19" s="2">
-        <f>IF($A19="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A19,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F19" s="2">
-        <f>IF($A19="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A19),""))</f>
-        <v/>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2">
-        <f>IF($A19="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A19),""))</f>
-        <v/>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2">
-        <f>IF($A19="","",IFERROR(ROUND(AVERAGE(I19:L19),1),""))</f>
-        <v/>
-      </c>
-      <c r="N19" s="2">
-        <f>IF(M19="","",IF(M19&gt;=4.2,"推荐",IF(M19&gt;=3.4,"可接受",IF(M19&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="2">
-        <f>IF(产品清单!A20="","",产品清单!A20)</f>
-        <v/>
-      </c>
-      <c r="B20" s="2">
-        <f>IF(产品清单!B20="","",产品清单!B20)</f>
-        <v/>
-      </c>
-      <c r="C20" s="2">
-        <f>IF(产品清单!C20="","",产品清单!C20)</f>
-        <v/>
-      </c>
-      <c r="D20" s="2">
-        <f>IF($A20="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A20,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E20" s="2">
-        <f>IF($A20="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A20,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F20" s="2">
-        <f>IF($A20="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A20),""))</f>
-        <v/>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2">
-        <f>IF($A20="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A20),""))</f>
-        <v/>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2">
-        <f>IF($A20="","",IFERROR(ROUND(AVERAGE(I20:L20),1),""))</f>
-        <v/>
-      </c>
-      <c r="N20" s="2">
-        <f>IF(M20="","",IF(M20&gt;=4.2,"推荐",IF(M20&gt;=3.4,"可接受",IF(M20&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="2">
-        <f>IF(产品清单!A21="","",产品清单!A21)</f>
-        <v/>
-      </c>
-      <c r="B21" s="2">
-        <f>IF(产品清单!B21="","",产品清单!B21)</f>
-        <v/>
-      </c>
-      <c r="C21" s="2">
-        <f>IF(产品清单!C21="","",产品清单!C21)</f>
-        <v/>
-      </c>
-      <c r="D21" s="2">
-        <f>IF($A21="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A21,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E21" s="2">
-        <f>IF($A21="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A21,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F21" s="2">
-        <f>IF($A21="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A21),""))</f>
-        <v/>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2">
-        <f>IF($A21="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A21),""))</f>
-        <v/>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2">
-        <f>IF($A21="","",IFERROR(ROUND(AVERAGE(I21:L21),1),""))</f>
-        <v/>
-      </c>
-      <c r="N21" s="2">
-        <f>IF(M21="","",IF(M21&gt;=4.2,"推荐",IF(M21&gt;=3.4,"可接受",IF(M21&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="2">
-        <f>IF(产品清单!A22="","",产品清单!A22)</f>
-        <v/>
-      </c>
-      <c r="B22" s="2">
-        <f>IF(产品清单!B22="","",产品清单!B22)</f>
-        <v/>
-      </c>
-      <c r="C22" s="2">
-        <f>IF(产品清单!C22="","",产品清单!C22)</f>
-        <v/>
-      </c>
-      <c r="D22" s="2">
-        <f>IF($A22="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A22,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E22" s="2">
-        <f>IF($A22="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A22,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F22" s="2">
-        <f>IF($A22="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A22),""))</f>
-        <v/>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2">
-        <f>IF($A22="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A22),""))</f>
-        <v/>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2">
-        <f>IF($A22="","",IFERROR(ROUND(AVERAGE(I22:L22),1),""))</f>
-        <v/>
-      </c>
-      <c r="N22" s="2">
-        <f>IF(M22="","",IF(M22&gt;=4.2,"推荐",IF(M22&gt;=3.4,"可接受",IF(M22&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O22" s="2" t="inlineStr"/>
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="2">
-        <f>IF(产品清单!A23="","",产品清单!A23)</f>
-        <v/>
-      </c>
-      <c r="B23" s="2">
-        <f>IF(产品清单!B23="","",产品清单!B23)</f>
-        <v/>
-      </c>
-      <c r="C23" s="2">
-        <f>IF(产品清单!C23="","",产品清单!C23)</f>
-        <v/>
-      </c>
-      <c r="D23" s="2">
-        <f>IF($A23="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A23,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E23" s="2">
-        <f>IF($A23="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A23,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F23" s="2">
-        <f>IF($A23="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A23),""))</f>
-        <v/>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2">
-        <f>IF($A23="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A23),""))</f>
-        <v/>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2">
-        <f>IF($A23="","",IFERROR(ROUND(AVERAGE(I23:L23),1),""))</f>
-        <v/>
-      </c>
-      <c r="N23" s="2">
-        <f>IF(M23="","",IF(M23&gt;=4.2,"推荐",IF(M23&gt;=3.4,"可接受",IF(M23&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O23" s="2" t="inlineStr"/>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="2">
-        <f>IF(产品清单!A24="","",产品清单!A24)</f>
-        <v/>
-      </c>
-      <c r="B24" s="2">
-        <f>IF(产品清单!B24="","",产品清单!B24)</f>
-        <v/>
-      </c>
-      <c r="C24" s="2">
-        <f>IF(产品清单!C24="","",产品清单!C24)</f>
-        <v/>
-      </c>
-      <c r="D24" s="2">
-        <f>IF($A24="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A24,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E24" s="2">
-        <f>IF($A24="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A24,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F24" s="2">
-        <f>IF($A24="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A24),""))</f>
-        <v/>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2">
-        <f>IF($A24="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A24),""))</f>
-        <v/>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2">
-        <f>IF($A24="","",IFERROR(ROUND(AVERAGE(I24:L24),1),""))</f>
-        <v/>
-      </c>
-      <c r="N24" s="2">
-        <f>IF(M24="","",IF(M24&gt;=4.2,"推荐",IF(M24&gt;=3.4,"可接受",IF(M24&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="2">
-        <f>IF(产品清单!A25="","",产品清单!A25)</f>
-        <v/>
-      </c>
-      <c r="B25" s="2">
-        <f>IF(产品清单!B25="","",产品清单!B25)</f>
-        <v/>
-      </c>
-      <c r="C25" s="2">
-        <f>IF(产品清单!C25="","",产品清单!C25)</f>
-        <v/>
-      </c>
-      <c r="D25" s="2">
-        <f>IF($A25="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A25,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E25" s="2">
-        <f>IF($A25="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A25,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F25" s="2">
-        <f>IF($A25="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A25),""))</f>
-        <v/>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2">
-        <f>IF($A25="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A25),""))</f>
-        <v/>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2">
-        <f>IF($A25="","",IFERROR(ROUND(AVERAGE(I25:L25),1),""))</f>
-        <v/>
-      </c>
-      <c r="N25" s="2">
-        <f>IF(M25="","",IF(M25&gt;=4.2,"推荐",IF(M25&gt;=3.4,"可接受",IF(M25&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="2">
-        <f>IF(产品清单!A26="","",产品清单!A26)</f>
-        <v/>
-      </c>
-      <c r="B26" s="2">
-        <f>IF(产品清单!B26="","",产品清单!B26)</f>
-        <v/>
-      </c>
-      <c r="C26" s="2">
-        <f>IF(产品清单!C26="","",产品清单!C26)</f>
-        <v/>
-      </c>
-      <c r="D26" s="2">
-        <f>IF($A26="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A26,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E26" s="2">
-        <f>IF($A26="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A26,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F26" s="2">
-        <f>IF($A26="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A26),""))</f>
-        <v/>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2">
-        <f>IF($A26="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A26),""))</f>
-        <v/>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2">
-        <f>IF($A26="","",IFERROR(ROUND(AVERAGE(I26:L26),1),""))</f>
-        <v/>
-      </c>
-      <c r="N26" s="2">
-        <f>IF(M26="","",IF(M26&gt;=4.2,"推荐",IF(M26&gt;=3.4,"可接受",IF(M26&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="2">
-        <f>IF(产品清单!A27="","",产品清单!A27)</f>
-        <v/>
-      </c>
-      <c r="B27" s="2">
-        <f>IF(产品清单!B27="","",产品清单!B27)</f>
-        <v/>
-      </c>
-      <c r="C27" s="2">
-        <f>IF(产品清单!C27="","",产品清单!C27)</f>
-        <v/>
-      </c>
-      <c r="D27" s="2">
-        <f>IF($A27="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A27,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E27" s="2">
-        <f>IF($A27="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A27,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F27" s="2">
-        <f>IF($A27="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A27),""))</f>
-        <v/>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2">
-        <f>IF($A27="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A27),""))</f>
-        <v/>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2">
-        <f>IF($A27="","",IFERROR(ROUND(AVERAGE(I27:L27),1),""))</f>
-        <v/>
-      </c>
-      <c r="N27" s="2">
-        <f>IF(M27="","",IF(M27&gt;=4.2,"推荐",IF(M27&gt;=3.4,"可接受",IF(M27&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="2">
-        <f>IF(产品清单!A28="","",产品清单!A28)</f>
-        <v/>
-      </c>
-      <c r="B28" s="2">
-        <f>IF(产品清单!B28="","",产品清单!B28)</f>
-        <v/>
-      </c>
-      <c r="C28" s="2">
-        <f>IF(产品清单!C28="","",产品清单!C28)</f>
-        <v/>
-      </c>
-      <c r="D28" s="2">
-        <f>IF($A28="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A28,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E28" s="2">
-        <f>IF($A28="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A28,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F28" s="2">
-        <f>IF($A28="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A28),""))</f>
-        <v/>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2">
-        <f>IF($A28="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A28),""))</f>
-        <v/>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2">
-        <f>IF($A28="","",IFERROR(ROUND(AVERAGE(I28:L28),1),""))</f>
-        <v/>
-      </c>
-      <c r="N28" s="2">
-        <f>IF(M28="","",IF(M28&gt;=4.2,"推荐",IF(M28&gt;=3.4,"可接受",IF(M28&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="2">
-        <f>IF(产品清单!A29="","",产品清单!A29)</f>
-        <v/>
-      </c>
-      <c r="B29" s="2">
-        <f>IF(产品清单!B29="","",产品清单!B29)</f>
-        <v/>
-      </c>
-      <c r="C29" s="2">
-        <f>IF(产品清单!C29="","",产品清单!C29)</f>
-        <v/>
-      </c>
-      <c r="D29" s="2">
-        <f>IF($A29="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A29,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E29" s="2">
-        <f>IF($A29="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A29,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F29" s="2">
-        <f>IF($A29="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A29),""))</f>
-        <v/>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2">
-        <f>IF($A29="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A29),""))</f>
-        <v/>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2">
-        <f>IF($A29="","",IFERROR(ROUND(AVERAGE(I29:L29),1),""))</f>
-        <v/>
-      </c>
-      <c r="N29" s="2">
-        <f>IF(M29="","",IF(M29&gt;=4.2,"推荐",IF(M29&gt;=3.4,"可接受",IF(M29&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O29" s="2" t="inlineStr"/>
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="2">
-        <f>IF(产品清单!A30="","",产品清单!A30)</f>
-        <v/>
-      </c>
-      <c r="B30" s="2">
-        <f>IF(产品清单!B30="","",产品清单!B30)</f>
-        <v/>
-      </c>
-      <c r="C30" s="2">
-        <f>IF(产品清单!C30="","",产品清单!C30)</f>
-        <v/>
-      </c>
-      <c r="D30" s="2">
-        <f>IF($A30="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A30,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E30" s="2">
-        <f>IF($A30="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A30,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F30" s="2">
-        <f>IF($A30="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A30),""))</f>
-        <v/>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2">
-        <f>IF($A30="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A30),""))</f>
-        <v/>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2">
-        <f>IF($A30="","",IFERROR(ROUND(AVERAGE(I30:L30),1),""))</f>
-        <v/>
-      </c>
-      <c r="N30" s="2">
-        <f>IF(M30="","",IF(M30&gt;=4.2,"推荐",IF(M30&gt;=3.4,"可接受",IF(M30&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O30" s="2" t="inlineStr"/>
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="2">
-        <f>IF(产品清单!A31="","",产品清单!A31)</f>
-        <v/>
-      </c>
-      <c r="B31" s="2">
-        <f>IF(产品清单!B31="","",产品清单!B31)</f>
-        <v/>
-      </c>
-      <c r="C31" s="2">
-        <f>IF(产品清单!C31="","",产品清单!C31)</f>
-        <v/>
-      </c>
-      <c r="D31" s="2">
-        <f>IF($A31="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A31,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E31" s="2">
-        <f>IF($A31="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A31,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F31" s="2">
-        <f>IF($A31="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A31),""))</f>
-        <v/>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2">
-        <f>IF($A31="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A31),""))</f>
-        <v/>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2">
-        <f>IF($A31="","",IFERROR(ROUND(AVERAGE(I31:L31),1),""))</f>
-        <v/>
-      </c>
-      <c r="N31" s="2">
-        <f>IF(M31="","",IF(M31&gt;=4.2,"推荐",IF(M31&gt;=3.4,"可接受",IF(M31&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O31" s="2" t="inlineStr"/>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="2">
-        <f>IF(产品清单!A32="","",产品清单!A32)</f>
-        <v/>
-      </c>
-      <c r="B32" s="2">
-        <f>IF(产品清单!B32="","",产品清单!B32)</f>
-        <v/>
-      </c>
-      <c r="C32" s="2">
-        <f>IF(产品清单!C32="","",产品清单!C32)</f>
-        <v/>
-      </c>
-      <c r="D32" s="2">
-        <f>IF($A32="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A32,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E32" s="2">
-        <f>IF($A32="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A32,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F32" s="2">
-        <f>IF($A32="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A32),""))</f>
-        <v/>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2">
-        <f>IF($A32="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A32),""))</f>
-        <v/>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2">
-        <f>IF($A32="","",IFERROR(ROUND(AVERAGE(I32:L32),1),""))</f>
-        <v/>
-      </c>
-      <c r="N32" s="2">
-        <f>IF(M32="","",IF(M32&gt;=4.2,"推荐",IF(M32&gt;=3.4,"可接受",IF(M32&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="2">
-        <f>IF(产品清单!A33="","",产品清单!A33)</f>
-        <v/>
-      </c>
-      <c r="B33" s="2">
-        <f>IF(产品清单!B33="","",产品清单!B33)</f>
-        <v/>
-      </c>
-      <c r="C33" s="2">
-        <f>IF(产品清单!C33="","",产品清单!C33)</f>
-        <v/>
-      </c>
-      <c r="D33" s="2">
-        <f>IF($A33="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A33,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E33" s="2">
-        <f>IF($A33="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A33,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F33" s="2">
-        <f>IF($A33="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A33),""))</f>
-        <v/>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2">
-        <f>IF($A33="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A33),""))</f>
-        <v/>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2">
-        <f>IF($A33="","",IFERROR(ROUND(AVERAGE(I33:L33),1),""))</f>
-        <v/>
-      </c>
-      <c r="N33" s="2">
-        <f>IF(M33="","",IF(M33&gt;=4.2,"推荐",IF(M33&gt;=3.4,"可接受",IF(M33&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O33" s="2" t="inlineStr"/>
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="2">
-        <f>IF(产品清单!A34="","",产品清单!A34)</f>
-        <v/>
-      </c>
-      <c r="B34" s="2">
-        <f>IF(产品清单!B34="","",产品清单!B34)</f>
-        <v/>
-      </c>
-      <c r="C34" s="2">
-        <f>IF(产品清单!C34="","",产品清单!C34)</f>
-        <v/>
-      </c>
-      <c r="D34" s="2">
-        <f>IF($A34="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A34,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E34" s="2">
-        <f>IF($A34="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A34,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F34" s="2">
-        <f>IF($A34="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A34),""))</f>
-        <v/>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2">
-        <f>IF($A34="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A34),""))</f>
-        <v/>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2">
-        <f>IF($A34="","",IFERROR(ROUND(AVERAGE(I34:L34),1),""))</f>
-        <v/>
-      </c>
-      <c r="N34" s="2">
-        <f>IF(M34="","",IF(M34&gt;=4.2,"推荐",IF(M34&gt;=3.4,"可接受",IF(M34&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O34" s="2" t="inlineStr"/>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="2">
-        <f>IF(产品清单!A35="","",产品清单!A35)</f>
-        <v/>
-      </c>
-      <c r="B35" s="2">
-        <f>IF(产品清单!B35="","",产品清单!B35)</f>
-        <v/>
-      </c>
-      <c r="C35" s="2">
-        <f>IF(产品清单!C35="","",产品清单!C35)</f>
-        <v/>
-      </c>
-      <c r="D35" s="2">
-        <f>IF($A35="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A35,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E35" s="2">
-        <f>IF($A35="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A35,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F35" s="2">
-        <f>IF($A35="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A35),""))</f>
-        <v/>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2">
-        <f>IF($A35="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A35),""))</f>
-        <v/>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2">
-        <f>IF($A35="","",IFERROR(ROUND(AVERAGE(I35:L35),1),""))</f>
-        <v/>
-      </c>
-      <c r="N35" s="2">
-        <f>IF(M35="","",IF(M35&gt;=4.2,"推荐",IF(M35&gt;=3.4,"可接受",IF(M35&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O35" s="2" t="inlineStr"/>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="2">
-        <f>IF(产品清单!A36="","",产品清单!A36)</f>
-        <v/>
-      </c>
-      <c r="B36" s="2">
-        <f>IF(产品清单!B36="","",产品清单!B36)</f>
-        <v/>
-      </c>
-      <c r="C36" s="2">
-        <f>IF(产品清单!C36="","",产品清单!C36)</f>
-        <v/>
-      </c>
-      <c r="D36" s="2">
-        <f>IF($A36="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A36,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E36" s="2">
-        <f>IF($A36="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A36,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F36" s="2">
-        <f>IF($A36="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A36),""))</f>
-        <v/>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2">
-        <f>IF($A36="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A36),""))</f>
-        <v/>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2">
-        <f>IF($A36="","",IFERROR(ROUND(AVERAGE(I36:L36),1),""))</f>
-        <v/>
-      </c>
-      <c r="N36" s="2">
-        <f>IF(M36="","",IF(M36&gt;=4.2,"推荐",IF(M36&gt;=3.4,"可接受",IF(M36&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="2">
-        <f>IF(产品清单!A37="","",产品清单!A37)</f>
-        <v/>
-      </c>
-      <c r="B37" s="2">
-        <f>IF(产品清单!B37="","",产品清单!B37)</f>
-        <v/>
-      </c>
-      <c r="C37" s="2">
-        <f>IF(产品清单!C37="","",产品清单!C37)</f>
-        <v/>
-      </c>
-      <c r="D37" s="2">
-        <f>IF($A37="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A37,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E37" s="2">
-        <f>IF($A37="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A37,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F37" s="2">
-        <f>IF($A37="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A37),""))</f>
-        <v/>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2">
-        <f>IF($A37="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A37),""))</f>
-        <v/>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2">
-        <f>IF($A37="","",IFERROR(ROUND(AVERAGE(I37:L37),1),""))</f>
-        <v/>
-      </c>
-      <c r="N37" s="2">
-        <f>IF(M37="","",IF(M37&gt;=4.2,"推荐",IF(M37&gt;=3.4,"可接受",IF(M37&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O37" s="2" t="inlineStr"/>
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="2">
-        <f>IF(产品清单!A38="","",产品清单!A38)</f>
-        <v/>
-      </c>
-      <c r="B38" s="2">
-        <f>IF(产品清单!B38="","",产品清单!B38)</f>
-        <v/>
-      </c>
-      <c r="C38" s="2">
-        <f>IF(产品清单!C38="","",产品清单!C38)</f>
-        <v/>
-      </c>
-      <c r="D38" s="2">
-        <f>IF($A38="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A38,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E38" s="2">
-        <f>IF($A38="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A38,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F38" s="2">
-        <f>IF($A38="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A38),""))</f>
-        <v/>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2">
-        <f>IF($A38="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A38),""))</f>
-        <v/>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2">
-        <f>IF($A38="","",IFERROR(ROUND(AVERAGE(I38:L38),1),""))</f>
-        <v/>
-      </c>
-      <c r="N38" s="2">
-        <f>IF(M38="","",IF(M38&gt;=4.2,"推荐",IF(M38&gt;=3.4,"可接受",IF(M38&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O38" s="2" t="inlineStr"/>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="2">
-        <f>IF(产品清单!A39="","",产品清单!A39)</f>
-        <v/>
-      </c>
-      <c r="B39" s="2">
-        <f>IF(产品清单!B39="","",产品清单!B39)</f>
-        <v/>
-      </c>
-      <c r="C39" s="2">
-        <f>IF(产品清单!C39="","",产品清单!C39)</f>
-        <v/>
-      </c>
-      <c r="D39" s="2">
-        <f>IF($A39="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A39,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E39" s="2">
-        <f>IF($A39="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A39,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F39" s="2">
-        <f>IF($A39="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A39),""))</f>
-        <v/>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2">
-        <f>IF($A39="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A39),""))</f>
-        <v/>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2">
-        <f>IF($A39="","",IFERROR(ROUND(AVERAGE(I39:L39),1),""))</f>
-        <v/>
-      </c>
-      <c r="N39" s="2">
-        <f>IF(M39="","",IF(M39&gt;=4.2,"推荐",IF(M39&gt;=3.4,"可接受",IF(M39&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O39" s="2" t="inlineStr"/>
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="2">
-        <f>IF(产品清单!A40="","",产品清单!A40)</f>
-        <v/>
-      </c>
-      <c r="B40" s="2">
-        <f>IF(产品清单!B40="","",产品清单!B40)</f>
-        <v/>
-      </c>
-      <c r="C40" s="2">
-        <f>IF(产品清单!C40="","",产品清单!C40)</f>
-        <v/>
-      </c>
-      <c r="D40" s="2">
-        <f>IF($A40="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A40,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E40" s="2">
-        <f>IF($A40="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A40,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F40" s="2">
-        <f>IF($A40="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A40),""))</f>
-        <v/>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2">
-        <f>IF($A40="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A40),""))</f>
-        <v/>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2">
-        <f>IF($A40="","",IFERROR(ROUND(AVERAGE(I40:L40),1),""))</f>
-        <v/>
-      </c>
-      <c r="N40" s="2">
-        <f>IF(M40="","",IF(M40&gt;=4.2,"推荐",IF(M40&gt;=3.4,"可接受",IF(M40&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O40" s="2" t="inlineStr"/>
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="2">
-        <f>IF(产品清单!A41="","",产品清单!A41)</f>
-        <v/>
-      </c>
-      <c r="B41" s="2">
-        <f>IF(产品清单!B41="","",产品清单!B41)</f>
-        <v/>
-      </c>
-      <c r="C41" s="2">
-        <f>IF(产品清单!C41="","",产品清单!C41)</f>
-        <v/>
-      </c>
-      <c r="D41" s="2">
-        <f>IF($A41="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A41,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E41" s="2">
-        <f>IF($A41="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A41,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F41" s="2">
-        <f>IF($A41="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A41),""))</f>
-        <v/>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2">
-        <f>IF($A41="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A41),""))</f>
-        <v/>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2">
-        <f>IF($A41="","",IFERROR(ROUND(AVERAGE(I41:L41),1),""))</f>
-        <v/>
-      </c>
-      <c r="N41" s="2">
-        <f>IF(M41="","",IF(M41&gt;=4.2,"推荐",IF(M41&gt;=3.4,"可接受",IF(M41&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O41" s="2" t="inlineStr"/>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="2">
-        <f>IF(产品清单!A42="","",产品清单!A42)</f>
-        <v/>
-      </c>
-      <c r="B42" s="2">
-        <f>IF(产品清单!B42="","",产品清单!B42)</f>
-        <v/>
-      </c>
-      <c r="C42" s="2">
-        <f>IF(产品清单!C42="","",产品清单!C42)</f>
-        <v/>
-      </c>
-      <c r="D42" s="2">
-        <f>IF($A42="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A42,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E42" s="2">
-        <f>IF($A42="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A42,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F42" s="2">
-        <f>IF($A42="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A42),""))</f>
-        <v/>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2">
-        <f>IF($A42="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A42),""))</f>
-        <v/>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2">
-        <f>IF($A42="","",IFERROR(ROUND(AVERAGE(I42:L42),1),""))</f>
-        <v/>
-      </c>
-      <c r="N42" s="2">
-        <f>IF(M42="","",IF(M42&gt;=4.2,"推荐",IF(M42&gt;=3.4,"可接受",IF(M42&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O42" s="2" t="inlineStr"/>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="2">
-        <f>IF(产品清单!A43="","",产品清单!A43)</f>
-        <v/>
-      </c>
-      <c r="B43" s="2">
-        <f>IF(产品清单!B43="","",产品清单!B43)</f>
-        <v/>
-      </c>
-      <c r="C43" s="2">
-        <f>IF(产品清单!C43="","",产品清单!C43)</f>
-        <v/>
-      </c>
-      <c r="D43" s="2">
-        <f>IF($A43="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A43,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E43" s="2">
-        <f>IF($A43="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A43,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F43" s="2">
-        <f>IF($A43="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A43),""))</f>
-        <v/>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2">
-        <f>IF($A43="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A43),""))</f>
-        <v/>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2">
-        <f>IF($A43="","",IFERROR(ROUND(AVERAGE(I43:L43),1),""))</f>
-        <v/>
-      </c>
-      <c r="N43" s="2">
-        <f>IF(M43="","",IF(M43&gt;=4.2,"推荐",IF(M43&gt;=3.4,"可接受",IF(M43&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O43" s="2" t="inlineStr"/>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="2">
-        <f>IF(产品清单!A44="","",产品清单!A44)</f>
-        <v/>
-      </c>
-      <c r="B44" s="2">
-        <f>IF(产品清单!B44="","",产品清单!B44)</f>
-        <v/>
-      </c>
-      <c r="C44" s="2">
-        <f>IF(产品清单!C44="","",产品清单!C44)</f>
-        <v/>
-      </c>
-      <c r="D44" s="2">
-        <f>IF($A44="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A44,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E44" s="2">
-        <f>IF($A44="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A44,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F44" s="2">
-        <f>IF($A44="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A44),""))</f>
-        <v/>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2">
-        <f>IF($A44="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A44),""))</f>
-        <v/>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2">
-        <f>IF($A44="","",IFERROR(ROUND(AVERAGE(I44:L44),1),""))</f>
-        <v/>
-      </c>
-      <c r="N44" s="2">
-        <f>IF(M44="","",IF(M44&gt;=4.2,"推荐",IF(M44&gt;=3.4,"可接受",IF(M44&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O44" s="2" t="inlineStr"/>
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="2">
-        <f>IF(产品清单!A45="","",产品清单!A45)</f>
-        <v/>
-      </c>
-      <c r="B45" s="2">
-        <f>IF(产品清单!B45="","",产品清单!B45)</f>
-        <v/>
-      </c>
-      <c r="C45" s="2">
-        <f>IF(产品清单!C45="","",产品清单!C45)</f>
-        <v/>
-      </c>
-      <c r="D45" s="2">
-        <f>IF($A45="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A45,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E45" s="2">
-        <f>IF($A45="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A45,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F45" s="2">
-        <f>IF($A45="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A45),""))</f>
-        <v/>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2">
-        <f>IF($A45="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A45),""))</f>
-        <v/>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2">
-        <f>IF($A45="","",IFERROR(ROUND(AVERAGE(I45:L45),1),""))</f>
-        <v/>
-      </c>
-      <c r="N45" s="2">
-        <f>IF(M45="","",IF(M45&gt;=4.2,"推荐",IF(M45&gt;=3.4,"可接受",IF(M45&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O45" s="2" t="inlineStr"/>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="2">
-        <f>IF(产品清单!A46="","",产品清单!A46)</f>
-        <v/>
-      </c>
-      <c r="B46" s="2">
-        <f>IF(产品清单!B46="","",产品清单!B46)</f>
-        <v/>
-      </c>
-      <c r="C46" s="2">
-        <f>IF(产品清单!C46="","",产品清单!C46)</f>
-        <v/>
-      </c>
-      <c r="D46" s="2">
-        <f>IF($A46="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A46,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E46" s="2">
-        <f>IF($A46="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A46,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F46" s="2">
-        <f>IF($A46="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A46),""))</f>
-        <v/>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2">
-        <f>IF($A46="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A46),""))</f>
-        <v/>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2">
-        <f>IF($A46="","",IFERROR(ROUND(AVERAGE(I46:L46),1),""))</f>
-        <v/>
-      </c>
-      <c r="N46" s="2">
-        <f>IF(M46="","",IF(M46&gt;=4.2,"推荐",IF(M46&gt;=3.4,"可接受",IF(M46&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O46" s="2" t="inlineStr"/>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="2">
-        <f>IF(产品清单!A47="","",产品清单!A47)</f>
-        <v/>
-      </c>
-      <c r="B47" s="2">
-        <f>IF(产品清单!B47="","",产品清单!B47)</f>
-        <v/>
-      </c>
-      <c r="C47" s="2">
-        <f>IF(产品清单!C47="","",产品清单!C47)</f>
-        <v/>
-      </c>
-      <c r="D47" s="2">
-        <f>IF($A47="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A47,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E47" s="2">
-        <f>IF($A47="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A47,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F47" s="2">
-        <f>IF($A47="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A47),""))</f>
-        <v/>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2">
-        <f>IF($A47="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A47),""))</f>
-        <v/>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2">
-        <f>IF($A47="","",IFERROR(ROUND(AVERAGE(I47:L47),1),""))</f>
-        <v/>
-      </c>
-      <c r="N47" s="2">
-        <f>IF(M47="","",IF(M47&gt;=4.2,"推荐",IF(M47&gt;=3.4,"可接受",IF(M47&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O47" s="2" t="inlineStr"/>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="2">
-        <f>IF(产品清单!A48="","",产品清单!A48)</f>
-        <v/>
-      </c>
-      <c r="B48" s="2">
-        <f>IF(产品清单!B48="","",产品清单!B48)</f>
-        <v/>
-      </c>
-      <c r="C48" s="2">
-        <f>IF(产品清单!C48="","",产品清单!C48)</f>
-        <v/>
-      </c>
-      <c r="D48" s="2">
-        <f>IF($A48="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A48,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E48" s="2">
-        <f>IF($A48="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A48,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F48" s="2">
-        <f>IF($A48="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A48),""))</f>
-        <v/>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2">
-        <f>IF($A48="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A48),""))</f>
-        <v/>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2">
-        <f>IF($A48="","",IFERROR(ROUND(AVERAGE(I48:L48),1),""))</f>
-        <v/>
-      </c>
-      <c r="N48" s="2">
-        <f>IF(M48="","",IF(M48&gt;=4.2,"推荐",IF(M48&gt;=3.4,"可接受",IF(M48&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O48" s="2" t="inlineStr"/>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="2">
-        <f>IF(产品清单!A49="","",产品清单!A49)</f>
-        <v/>
-      </c>
-      <c r="B49" s="2">
-        <f>IF(产品清单!B49="","",产品清单!B49)</f>
-        <v/>
-      </c>
-      <c r="C49" s="2">
-        <f>IF(产品清单!C49="","",产品清单!C49)</f>
-        <v/>
-      </c>
-      <c r="D49" s="2">
-        <f>IF($A49="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A49,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E49" s="2">
-        <f>IF($A49="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A49,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F49" s="2">
-        <f>IF($A49="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A49),""))</f>
-        <v/>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2">
-        <f>IF($A49="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A49),""))</f>
-        <v/>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2">
-        <f>IF($A49="","",IFERROR(ROUND(AVERAGE(I49:L49),1),""))</f>
-        <v/>
-      </c>
-      <c r="N49" s="2">
-        <f>IF(M49="","",IF(M49&gt;=4.2,"推荐",IF(M49&gt;=3.4,"可接受",IF(M49&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O49" s="2" t="inlineStr"/>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="2">
-        <f>IF(产品清单!A50="","",产品清单!A50)</f>
-        <v/>
-      </c>
-      <c r="B50" s="2">
-        <f>IF(产品清单!B50="","",产品清单!B50)</f>
-        <v/>
-      </c>
-      <c r="C50" s="2">
-        <f>IF(产品清单!C50="","",产品清单!C50)</f>
-        <v/>
-      </c>
-      <c r="D50" s="2">
-        <f>IF($A50="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A50,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E50" s="2">
-        <f>IF($A50="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A50,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F50" s="2">
-        <f>IF($A50="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A50),""))</f>
-        <v/>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2">
-        <f>IF($A50="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A50),""))</f>
-        <v/>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2">
-        <f>IF($A50="","",IFERROR(ROUND(AVERAGE(I50:L50),1),""))</f>
-        <v/>
-      </c>
-      <c r="N50" s="2">
-        <f>IF(M50="","",IF(M50&gt;=4.2,"推荐",IF(M50&gt;=3.4,"可接受",IF(M50&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O50" s="2" t="inlineStr"/>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="2">
-        <f>IF(产品清单!A51="","",产品清单!A51)</f>
-        <v/>
-      </c>
-      <c r="B51" s="2">
-        <f>IF(产品清单!B51="","",产品清单!B51)</f>
-        <v/>
-      </c>
-      <c r="C51" s="2">
-        <f>IF(产品清单!C51="","",产品清单!C51)</f>
-        <v/>
-      </c>
-      <c r="D51" s="2">
-        <f>IF($A51="","",IFERROR(AVERAGEIFS(场景记录!J:J,场景记录!B:B,$A51,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="E51" s="2">
-        <f>IF($A51="","",IFERROR(AVERAGEIFS(场景记录!M:M,场景记录!B:B,$A51,场景记录!D:D,"空闲常驻"),""))</f>
-        <v/>
-      </c>
-      <c r="F51" s="2">
-        <f>IF($A51="","",IFERROR(MAXIFS(场景记录!P:P,场景记录!B:B,$A51),""))</f>
-        <v/>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2">
-        <f>IF($A51="","",IFERROR(AVERAGEIFS(场景记录!Z:Z,场景记录!B:B,$A51),""))</f>
-        <v/>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2">
-        <f>IF($A51="","",IFERROR(ROUND(AVERAGE(I51:L51),1),""))</f>
-        <v/>
-      </c>
-      <c r="N51" s="2">
-        <f>IF(M51="","",IF(M51&gt;=4.2,"推荐",IF(M51&gt;=3.4,"可接受",IF(M51&gt;=2.6,"谨慎","不推荐"))))</f>
-        <v/>
-      </c>
-      <c r="O51" s="2" t="inlineStr"/>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="N2:N51">
@@ -6517,7 +9614,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>powershell -ExecutionPolicy Bypass -File D:\desktop_pet\tools\collect_desktop_pet_perf.ps1 -ProductId P001 -ProductName BongoCat -ProcessName BongoCat -Scenario 空闲常驻 -DurationSec 600</t>
+          <t>powershell -ExecutionPolicy Bypass -File D:\desktop_pet\tools\collect_desktop_pet_perf.ps1 -ProductId P001 -ProductName BongoCat -ProcessName bongo-cat -Scenario 空闲常驻 -DurationSec 600</t>
         </is>
       </c>
     </row>
